--- a/exp_m3_out/assist_09/module3_full.xlsx
+++ b/exp_m3_out/assist_09/module3_full.xlsx
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7890393041217743</v>
+        <v>0.7890393081496887</v>
       </c>
       <c r="D2" t="n">
         <v>0.742868560771851</v>
@@ -488,7 +488,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7881541562259231</v>
+        <v>0.7881541610594204</v>
       </c>
       <c r="D3" t="n">
         <v>0.7416125901539515</v>
@@ -507,7 +507,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.788128935036787</v>
+        <v>0.7881289148972148</v>
       </c>
       <c r="D4" t="n">
         <v>0.7418219185902681</v>
@@ -526,7 +526,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7883338124886661</v>
+        <v>0.7883337955714254</v>
       </c>
       <c r="D5" t="n">
         <v>0.741917067879503</v>
@@ -545,13 +545,13 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7880946381508067</v>
+        <v>0.7880946454010528</v>
       </c>
       <c r="D6" t="n">
         <v>0.7416696797274924</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4588884456299223</v>
+        <v>0.4588884293937743</v>
       </c>
     </row>
     <row r="7">
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.789039312983186</v>
+        <v>0.7890393065385228</v>
       </c>
       <c r="D7" t="n">
         <v>0.742868560771851</v>
@@ -583,13 +583,13 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7816478595660988</v>
+        <v>0.7816478466767726</v>
       </c>
       <c r="D8" t="n">
         <v>0.733410721421911</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4677591660140256</v>
+        <v>0.4677591500857846</v>
       </c>
     </row>
     <row r="9">
@@ -602,7 +602,7 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7817709171861207</v>
+        <v>0.7817709123526235</v>
       </c>
       <c r="D9" t="n">
         <v>0.7345144531770348</v>
@@ -621,7 +621,7 @@
         <v>0.3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7821137579582447</v>
+        <v>0.7821137619861591</v>
       </c>
       <c r="D10" t="n">
         <v>0.7339245275837789</v>
@@ -640,7 +640,7 @@
         <v>0.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7828807461780481</v>
+        <v>0.7828807477892139</v>
       </c>
       <c r="D11" t="n">
         <v>0.7355991550743116</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.78903930573294</v>
+        <v>0.7890393065385228</v>
       </c>
       <c r="D2" t="n">
         <v>0.742868560771851</v>
@@ -719,7 +719,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7827509627464734</v>
+        <v>0.7827509667743878</v>
       </c>
       <c r="D3" t="n">
         <v>0.7371596034177624</v>
@@ -738,7 +738,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7830391358580647</v>
+        <v>0.7830391366636476</v>
       </c>
       <c r="D4" t="n">
         <v>0.7369502749814459</v>
@@ -757,7 +757,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7831791880547447</v>
+        <v>0.7831791944994079</v>
       </c>
       <c r="D5" t="n">
         <v>0.7376163200060896</v>
@@ -776,7 +776,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7829467540289303</v>
+        <v>0.7829467483898501</v>
       </c>
       <c r="D6" t="n">
         <v>0.7370073645549867</v>
@@ -860,7 +860,7 @@
         <v>0.1512454623039485</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2622992006933352</v>
+        <v>0.262299051948838</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -888,10 +888,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3665779495083951</v>
+        <v>0.3665779105887953</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8794536705151206</v>
+        <v>0.8794533908837991</v>
       </c>
       <c r="F3" t="n">
         <v>0.6</v>
@@ -919,10 +919,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4126298599703341</v>
+        <v>0.4126298870391077</v>
       </c>
       <c r="E4" t="n">
-        <v>1.059851743586969</v>
+        <v>1.059851815637913</v>
       </c>
       <c r="F4" t="n">
         <v>0.6</v>
@@ -950,10 +950,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.164174928531702</v>
+        <v>1.164175242359223</v>
       </c>
       <c r="E5" t="n">
-        <v>1.646391972904262</v>
+        <v>1.646392416723398</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2947379076618787</v>
+        <v>0.2947378884787238</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6634142162050884</v>
+        <v>0.6634143915628818</v>
       </c>
       <c r="F6" t="n">
         <v>0.1666666666666667</v>
@@ -1012,10 +1012,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5810276341047247</v>
+        <v>0.5810277982390522</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8006089401609727</v>
+        <v>0.8006091052815862</v>
       </c>
       <c r="F7" t="n">
         <v>0.5</v>
@@ -1043,10 +1043,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6266991391997607</v>
+        <v>0.6266990036328378</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9773088509042218</v>
+        <v>0.9773088227445389</v>
       </c>
       <c r="F8" t="n">
         <v>0.6</v>
@@ -1074,10 +1074,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.820025919476753</v>
+        <v>1.820025035523151</v>
       </c>
       <c r="E9" t="n">
-        <v>1.820025440378694</v>
+        <v>1.820025035523151</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1105,10 +1105,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5339240586124773</v>
+        <v>0.5339241585036881</v>
       </c>
       <c r="E10" t="n">
-        <v>1.101833844101001</v>
+        <v>1.101833304153173</v>
       </c>
       <c r="F10" t="n">
         <v>0.25</v>
@@ -1167,10 +1167,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8302776871734037</v>
+        <v>0.8302776347254063</v>
       </c>
       <c r="E12" t="n">
-        <v>1.09616827201868</v>
+        <v>1.096167900877571</v>
       </c>
       <c r="F12" t="n">
         <v>0.5</v>
@@ -1229,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3932335106976957</v>
+        <v>0.3932334325526721</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9284424017756427</v>
+        <v>0.9284421527170117</v>
       </c>
       <c r="F14" t="n">
         <v>0.5</v>
@@ -1291,10 +1291,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.074116377641236</v>
+        <v>1.07411628378299</v>
       </c>
       <c r="E16" t="n">
-        <v>1.107676931393421</v>
+        <v>1.1076768098934</v>
       </c>
       <c r="F16" t="n">
         <v>0.75</v>
@@ -1322,10 +1322,10 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1572668994481585</v>
+        <v>0.1572667091758251</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3438597261294881</v>
+        <v>0.3438594235974431</v>
       </c>
       <c r="F17" t="n">
         <v>0.5</v>
@@ -1353,10 +1353,10 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1.802842950254579</v>
+        <v>1.802843263687091</v>
       </c>
       <c r="E18" t="n">
-        <v>1.850771897502861</v>
+        <v>1.850772174971763</v>
       </c>
       <c r="F18" t="n">
         <v>0.8</v>
@@ -1384,10 +1384,10 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6614573166901744</v>
+        <v>0.6614575383107535</v>
       </c>
       <c r="E19" t="n">
-        <v>1.03061307095536</v>
+        <v>1.030613358629495</v>
       </c>
       <c r="F19" t="n">
         <v>0.5714285714285714</v>
@@ -1446,10 +1446,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3131733545839463</v>
+        <v>0.3131733545348676</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6057024355836084</v>
+        <v>0.6057027813450842</v>
       </c>
       <c r="F21" t="n">
         <v>0.25</v>
@@ -1477,10 +1477,10 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2325603608795973</v>
+        <v>0.2325603317189987</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4073508621068977</v>
+        <v>0.4073508023766486</v>
       </c>
       <c r="F22" t="n">
         <v>0.6666666666666666</v>
@@ -1539,10 +1539,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7593041903995326</v>
+        <v>0.7593043199819414</v>
       </c>
       <c r="E24" t="n">
-        <v>1.082287744236197</v>
+        <v>1.082287726579716</v>
       </c>
       <c r="F24" t="n">
         <v>0.3333333333333333</v>
@@ -1570,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1467885221787933</v>
+        <v>0.1467885937824474</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2757261073061454</v>
+        <v>0.2757260573020227</v>
       </c>
       <c r="F25" t="n">
         <v>0.625</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6948922870856139</v>
+        <v>0.6948923755860803</v>
       </c>
       <c r="E26" t="n">
-        <v>1.034101741434367</v>
+        <v>1.034101812659773</v>
       </c>
       <c r="F26" t="n">
         <v>0.5</v>
@@ -1694,10 +1694,10 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2417924445422456</v>
+        <v>0.2417924614058327</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3228807327224787</v>
+        <v>0.322880799875741</v>
       </c>
       <c r="F29" t="n">
         <v>0.8333333333333334</v>
@@ -1725,10 +1725,10 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6579942660513161</v>
+        <v>0.6579942660673499</v>
       </c>
       <c r="E30" t="n">
-        <v>1.304108483898316</v>
+        <v>1.304108444704827</v>
       </c>
       <c r="F30" t="n">
         <v>0.375</v>
@@ -1756,10 +1756,10 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2868627957184234</v>
+        <v>0.2868629209896341</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3654667377870748</v>
+        <v>0.3654669458827619</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3358062127874999</v>
+        <v>0.3358061851252593</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8003483941658169</v>
+        <v>0.8003483650063025</v>
       </c>
       <c r="F32" t="n">
         <v>0.4</v>
@@ -1818,10 +1818,10 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3939819589630262</v>
+        <v>0.393981809686489</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6911485564182528</v>
+        <v>0.691148281041866</v>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
@@ -1849,10 +1849,10 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>1.068791759843806</v>
+        <v>1.06879163493145</v>
       </c>
       <c r="E34" t="n">
-        <v>1.211064729577703</v>
+        <v>1.211064732355489</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -1880,10 +1880,10 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7733113227830609</v>
+        <v>0.7733114650171818</v>
       </c>
       <c r="E35" t="n">
-        <v>1.531102767396739</v>
+        <v>1.531102848439988</v>
       </c>
       <c r="F35" t="n">
         <v>0.4285714285714285</v>
@@ -1911,10 +1911,10 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.871297071280044</v>
+        <v>0.8712971515377973</v>
       </c>
       <c r="E36" t="n">
-        <v>1.716906896360486</v>
+        <v>1.716907094432355</v>
       </c>
       <c r="F36" t="n">
         <v>0.6666666666666666</v>
@@ -1942,10 +1942,10 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1096831834828954</v>
+        <v>0.1096832290192276</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2094090959585715</v>
+        <v>0.2094091202292168</v>
       </c>
       <c r="F37" t="n">
         <v>0.25</v>
@@ -1973,10 +1973,10 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2754347186975684</v>
+        <v>0.2754344954877601</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5164921521816376</v>
+        <v>0.5164917289049058</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2035,10 +2035,10 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8349245093612052</v>
+        <v>0.8349259038524396</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5439122024927462</v>
+        <v>0.5439125060836224</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -2066,10 +2066,10 @@
         <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5821342054302754</v>
+        <v>0.5821341735003559</v>
       </c>
       <c r="E41" t="n">
-        <v>1.242795561751142</v>
+        <v>1.242795466974643</v>
       </c>
       <c r="F41" t="n">
         <v>0.8333333333333334</v>
@@ -2097,10 +2097,10 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1.221360705375979</v>
+        <v>1.22136039326929</v>
       </c>
       <c r="E42" t="n">
-        <v>1.134871172873483</v>
+        <v>1.134870643930354</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -2128,10 +2128,10 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3605628381305232</v>
+        <v>0.3605627848364238</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5099128557719208</v>
+        <v>0.5099127804026827</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2190,10 +2190,10 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.653998661650578</v>
+        <v>0.6539989534793594</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9248878012453398</v>
+        <v>0.9248884036647168</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -2221,10 +2221,10 @@
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4141946023604042</v>
+        <v>0.4141946459744819</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4576234049397385</v>
+        <v>0.4576237412730391</v>
       </c>
       <c r="F46" t="n">
         <v>0.5</v>
@@ -2252,10 +2252,10 @@
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2137474974429773</v>
+        <v>0.2137469395749997</v>
       </c>
       <c r="E47" t="n">
-        <v>0.257483998705387</v>
+        <v>0.2574828217854094</v>
       </c>
       <c r="F47" t="n">
         <v>0.75</v>
@@ -2314,10 +2314,10 @@
         <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.430791925441434</v>
+        <v>0.4307918310911045</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9136876909897864</v>
+        <v>0.9136874803474795</v>
       </c>
       <c r="F49" t="n">
         <v>0.1</v>
@@ -2345,10 +2345,10 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>0.483924548152072</v>
+        <v>0.4839245650548916</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6889506562491894</v>
+        <v>0.6889510611986562</v>
       </c>
       <c r="F50" t="n">
         <v>0.5</v>
@@ -2376,10 +2376,10 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2065908608609648</v>
+        <v>0.2065907977680043</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6771740757299231</v>
+        <v>0.6771740960412056</v>
       </c>
       <c r="F51" t="n">
         <v>0.25</v>
@@ -2407,10 +2407,10 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0.04552059791379226</v>
+        <v>0.04552073724158889</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0748994040179343</v>
+        <v>0.07489964516880365</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2469,10 +2469,10 @@
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2060721002580007</v>
+        <v>0.2060720888386464</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3841526428386003</v>
+        <v>0.3841527663590047</v>
       </c>
       <c r="F54" t="n">
         <v>0.2</v>
@@ -2500,10 +2500,10 @@
         <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6564155860156777</v>
+        <v>0.6564154689493108</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9934294610855672</v>
+        <v>0.9934293712575428</v>
       </c>
       <c r="F55" t="n">
         <v>0.5</v>
@@ -2531,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4458765660993487</v>
+        <v>0.4458768395986037</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8597231614983259</v>
+        <v>0.8597229848814161</v>
       </c>
       <c r="F56" t="n">
         <v>0.3333333333333333</v>
@@ -2562,10 +2562,10 @@
         <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2278453943268237</v>
+        <v>0.2278455568369794</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3952253306947098</v>
+        <v>0.3952255607300867</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0.9845286823180112</v>
       </c>
       <c r="E58" t="n">
-        <v>1.705252456145356</v>
+        <v>1.705253699283634</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2624,10 +2624,10 @@
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9618049141044182</v>
+        <v>0.9618048179813201</v>
       </c>
       <c r="E59" t="n">
-        <v>1.087387964434381</v>
+        <v>1.087387882801208</v>
       </c>
       <c r="F59" t="n">
         <v>0.6</v>
@@ -2655,10 +2655,10 @@
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3087766660122302</v>
+        <v>0.30877678060252</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8292223872303068</v>
+        <v>0.8292226245126313</v>
       </c>
       <c r="F60" t="n">
         <v>0.5</v>
@@ -2686,10 +2686,10 @@
         <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3769034162142006</v>
+        <v>0.3769033841824277</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8513880430344661</v>
+        <v>0.8513879242257244</v>
       </c>
       <c r="F61" t="n">
         <v>0.7142857142857143</v>
@@ -2717,10 +2717,10 @@
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5254789596596172</v>
+        <v>0.5254788345817517</v>
       </c>
       <c r="E62" t="n">
-        <v>0.761760124462047</v>
+        <v>0.7617600602111718</v>
       </c>
       <c r="F62" t="n">
         <v>0.5</v>
@@ -2810,10 +2810,10 @@
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5015924526652841</v>
+        <v>0.5015926169786025</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6462016617923674</v>
+        <v>0.6462015480017788</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -2872,10 +2872,10 @@
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>0.602265771888275</v>
+        <v>0.6022658498830809</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6870130388310738</v>
+        <v>0.6870130788359364</v>
       </c>
       <c r="F67" t="n">
         <v>0.25</v>
@@ -2903,10 +2903,10 @@
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2234388452272563</v>
+        <v>0.2234387748212247</v>
       </c>
       <c r="E68" t="n">
-        <v>0.312900126199066</v>
+        <v>0.3129002344107999</v>
       </c>
       <c r="F68" t="n">
         <v>0.8</v>
@@ -2934,10 +2934,10 @@
         <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7260090479191275</v>
+        <v>0.7260096557679531</v>
       </c>
       <c r="E69" t="n">
-        <v>1.422460744654516</v>
+        <v>1.422460649132467</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -3027,10 +3027,10 @@
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9746138200997226</v>
+        <v>0.9746139790455141</v>
       </c>
       <c r="E72" t="n">
-        <v>1.379999605104415</v>
+        <v>1.379999843230161</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -3089,10 +3089,10 @@
         <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4034092500146853</v>
+        <v>0.4034092501247475</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8652349082543749</v>
+        <v>0.865234879003013</v>
       </c>
       <c r="F74" t="n">
         <v>0.6363636363636364</v>
@@ -3120,10 +3120,10 @@
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2426271173241734</v>
+        <v>0.2426269825847614</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5092265943875799</v>
+        <v>0.5092266131893793</v>
       </c>
       <c r="F75" t="n">
         <v>0.4285714285714285</v>
@@ -3151,10 +3151,10 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8215112237637013</v>
+        <v>0.8215114695844962</v>
       </c>
       <c r="E76" t="n">
-        <v>1.163786850254521</v>
+        <v>1.163786982683113</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6830617561877966</v>
+        <v>0.6830617511407713</v>
       </c>
       <c r="E77" t="n">
-        <v>1.185125074255353</v>
+        <v>1.185124990950685</v>
       </c>
       <c r="F77" t="n">
         <v>0.5</v>
@@ -3216,7 +3216,7 @@
         <v>0.5325166329552899</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5323949298274873</v>
+        <v>0.5323952986381477</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -3244,10 +3244,10 @@
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8428855758260086</v>
+        <v>0.8428855474211842</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9179165094010965</v>
+        <v>0.9179165916671421</v>
       </c>
       <c r="F79" t="n">
         <v>0.5</v>
@@ -3275,10 +3275,10 @@
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1.568817595892609</v>
+        <v>1.568817539326567</v>
       </c>
       <c r="E80" t="n">
-        <v>1.703781904537957</v>
+        <v>1.703782096193059</v>
       </c>
       <c r="F80" t="n">
         <v>0.8888888888888888</v>
@@ -3306,10 +3306,10 @@
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7461501195041803</v>
+        <v>0.7461500791727582</v>
       </c>
       <c r="E81" t="n">
-        <v>1.447442122261262</v>
+        <v>1.447442143944594</v>
       </c>
       <c r="F81" t="n">
         <v>0.5</v>
@@ -3368,10 +3368,10 @@
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2698850894191498</v>
+        <v>0.2698860354951864</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4267530875787152</v>
+        <v>0.4267535511944286</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -3399,10 +3399,10 @@
         <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8265397014218795</v>
+        <v>0.8265396150544647</v>
       </c>
       <c r="E84" t="n">
-        <v>1.474801493935096</v>
+        <v>1.474801397732338</v>
       </c>
       <c r="F84" t="n">
         <v>0.25</v>
@@ -3461,10 +3461,10 @@
         <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4335690840905552</v>
+        <v>0.433568826656111</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7519577362946955</v>
+        <v>0.7519572462299687</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -3492,10 +3492,10 @@
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5697169591840894</v>
+        <v>0.5697174091192414</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6769121732375347</v>
+        <v>0.6769127682192484</v>
       </c>
       <c r="F87" t="n">
         <v>0.8</v>
@@ -3523,10 +3523,10 @@
         <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4355252546321182</v>
+        <v>0.435524497822851</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7882758721433158</v>
+        <v>0.7882752907013781</v>
       </c>
       <c r="F88" t="n">
         <v>0.75</v>
@@ -3616,10 +3616,10 @@
         <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5236078271531702</v>
+        <v>0.5236079014129449</v>
       </c>
       <c r="E91" t="n">
-        <v>1.056716083103911</v>
+        <v>1.056716263435691</v>
       </c>
       <c r="F91" t="n">
         <v>0.5</v>
@@ -3647,10 +3647,10 @@
         <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>0.6257782062060964</v>
+        <v>0.625778464766046</v>
       </c>
       <c r="E92" t="n">
-        <v>1.14934600205406</v>
+        <v>1.149346052959257</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -3678,10 +3678,10 @@
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0.7547900069100598</v>
+        <v>0.7547900801857979</v>
       </c>
       <c r="E93" t="n">
-        <v>0.8467601443396876</v>
+        <v>0.8467600456477413</v>
       </c>
       <c r="F93" t="n">
         <v>0.75</v>
@@ -3740,10 +3740,10 @@
         <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7294593618148079</v>
+        <v>0.7294591607934515</v>
       </c>
       <c r="E95" t="n">
-        <v>1.280740724723295</v>
+        <v>1.280740303461457</v>
       </c>
       <c r="F95" t="n">
         <v>0.5</v>
@@ -3833,10 +3833,10 @@
         <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>0.546404465340859</v>
+        <v>0.5464043429772827</v>
       </c>
       <c r="E98" t="n">
-        <v>0.8093647396276721</v>
+        <v>0.8093644616848999</v>
       </c>
       <c r="F98" t="n">
         <v>0.75</v>
@@ -3895,10 +3895,10 @@
         <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3516396112624439</v>
+        <v>0.3516395703638803</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7926036925829478</v>
+        <v>0.7926036917034052</v>
       </c>
       <c r="F100" t="n">
         <v>0.6</v>
@@ -3926,10 +3926,10 @@
         <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>0.8778882718646793</v>
+        <v>0.8778884288060094</v>
       </c>
       <c r="E101" t="n">
-        <v>1.371292273335747</v>
+        <v>1.371291809238885</v>
       </c>
       <c r="F101" t="n">
         <v>0.6666666666666666</v>
@@ -3957,10 +3957,10 @@
         <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>0.6646636289753839</v>
+        <v>0.6646639050604523</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9893360901722753</v>
+        <v>0.9893360644734536</v>
       </c>
       <c r="F102" t="n">
         <v>0.5</v>
@@ -3988,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4907249073507122</v>
+        <v>0.4907250631812496</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8652949075122536</v>
+        <v>0.8652948430253676</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -4019,10 +4019,10 @@
         <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4481563811908141</v>
+        <v>0.4481564418779246</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7292405822887335</v>
+        <v>0.7292406805921796</v>
       </c>
       <c r="F104" t="n">
         <v>0.4</v>
@@ -4050,10 +4050,10 @@
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4003426095005611</v>
+        <v>0.4003426385086362</v>
       </c>
       <c r="E105" t="n">
-        <v>0.7994447299589749</v>
+        <v>0.7994445252164643</v>
       </c>
       <c r="F105" t="n">
         <v>0.4285714285714285</v>
@@ -4081,10 +4081,10 @@
         <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1.053098213270932</v>
+        <v>1.053106245361583</v>
       </c>
       <c r="E106" t="n">
-        <v>1.489284735338702</v>
+        <v>1.489295235651686</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -4112,10 +4112,10 @@
         <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3651048647302784</v>
+        <v>0.3651048489637302</v>
       </c>
       <c r="E107" t="n">
-        <v>0.7158762883096009</v>
+        <v>0.7158761222038219</v>
       </c>
       <c r="F107" t="n">
         <v>0.3333333333333333</v>
@@ -4143,10 +4143,10 @@
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1.28910531954028</v>
+        <v>1.289105186533281</v>
       </c>
       <c r="E108" t="n">
-        <v>1.492899841292548</v>
+        <v>1.492899631571105</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2717059563978726</v>
+        <v>0.2717059063219706</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3925145005919031</v>
+        <v>0.3925146057957392</v>
       </c>
       <c r="F109" t="n">
         <v>0.4444444444444444</v>
@@ -4236,10 +4236,10 @@
         <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2608576643854121</v>
+        <v>0.2608577284606146</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5241623016225093</v>
+        <v>0.5241623260022176</v>
       </c>
       <c r="F111" t="n">
         <v>0.3333333333333333</v>
@@ -4298,10 +4298,10 @@
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>0.8759215212788077</v>
+        <v>0.8759215031954803</v>
       </c>
       <c r="E113" t="n">
-        <v>0.934308978811326</v>
+        <v>0.9343091793450514</v>
       </c>
       <c r="F113" t="n">
         <v>0.6666666666666666</v>
@@ -4332,7 +4332,7 @@
         <v>0.4626486138908843</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8013309053103278</v>
+        <v>0.8013303737706914</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -4422,10 +4422,10 @@
         <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3236871497797043</v>
+        <v>0.323687096952107</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9323578020592547</v>
+        <v>0.9323578966101078</v>
       </c>
       <c r="F117" t="n">
         <v>0.6666666666666666</v>
@@ -4453,10 +4453,10 @@
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9791499735820035</v>
+        <v>0.979149367688778</v>
       </c>
       <c r="E118" t="n">
-        <v>1.441597878777974</v>
+        <v>1.441597160466</v>
       </c>
       <c r="F118" t="n">
         <v>0.5</v>
@@ -4546,10 +4546,10 @@
         <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>0.6189353683332651</v>
+        <v>0.6189353062504616</v>
       </c>
       <c r="E121" t="n">
-        <v>1.176943625803688</v>
+        <v>1.176943636306105</v>
       </c>
       <c r="F121" t="n">
         <v>0.4285714285714285</v>
@@ -4577,10 +4577,10 @@
         <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3308459425333896</v>
+        <v>0.3308459997987168</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7623068908524685</v>
+        <v>0.7623070643486329</v>
       </c>
       <c r="F122" t="n">
         <v>0.6666666666666666</v>
@@ -4670,10 +4670,10 @@
         <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6013164134183953</v>
+        <v>0.6013162571649767</v>
       </c>
       <c r="E125" t="n">
-        <v>1.034966877423227</v>
+        <v>1.034966965488212</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -4701,10 +4701,10 @@
         <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>0.5693492223404807</v>
+        <v>0.5693492570631757</v>
       </c>
       <c r="E126" t="n">
-        <v>1.07685016539181</v>
+        <v>1.076850238901283</v>
       </c>
       <c r="F126" t="n">
         <v>0.4</v>
@@ -4732,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>0.7682210742424125</v>
+        <v>0.7682209693879953</v>
       </c>
       <c r="E127" t="n">
-        <v>1.205031125422259</v>
+        <v>1.205031155722712</v>
       </c>
       <c r="F127" t="n">
         <v>0.8</v>
@@ -4794,10 +4794,10 @@
         <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4996647651019629</v>
+        <v>0.4996647782967007</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7066326874471627</v>
+        <v>0.7066327061073397</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
         <v>0.5302713284087134</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8046893269970947</v>
+        <v>0.8046893103169499</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -4856,10 +4856,10 @@
         <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3212498183789169</v>
+        <v>0.3212498696766594</v>
       </c>
       <c r="E131" t="n">
-        <v>0.7162846430621156</v>
+        <v>0.7162847476057781</v>
       </c>
       <c r="F131" t="n">
         <v>0.5</v>
@@ -4887,10 +4887,10 @@
         <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5841738795074347</v>
+        <v>0.5841736981211109</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8358497894944948</v>
+        <v>0.8358494479675297</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>4</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2759743202439149</v>
+        <v>0.2759744771756603</v>
       </c>
       <c r="E133" t="n">
-        <v>0.7205204373907567</v>
+        <v>0.7205203497432745</v>
       </c>
       <c r="F133" t="n">
         <v>0.3333333333333333</v>
@@ -4949,10 +4949,10 @@
         <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>1.36142292564731</v>
+        <v>1.361423223519205</v>
       </c>
       <c r="E134" t="n">
-        <v>1.925342765576084</v>
+        <v>1.925343186830558</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
@@ -4980,10 +4980,10 @@
         <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>0.618214580426261</v>
+        <v>0.6182144264844321</v>
       </c>
       <c r="E135" t="n">
-        <v>0.9159941343896877</v>
+        <v>0.9159939767038918</v>
       </c>
       <c r="F135" t="n">
         <v>0.75</v>
@@ -5011,10 +5011,10 @@
         <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9542009235960202</v>
+        <v>0.9542011368845107</v>
       </c>
       <c r="E136" t="n">
-        <v>1.527235714521042</v>
+        <v>1.527235829548379</v>
       </c>
       <c r="F136" t="n">
         <v>0.6</v>
@@ -5042,10 +5042,10 @@
         <v>4</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2545124018004046</v>
+        <v>0.2545113639162199</v>
       </c>
       <c r="E137" t="n">
-        <v>0.5558671554877486</v>
+        <v>0.5558669968727968</v>
       </c>
       <c r="F137" t="n">
         <v>0.4</v>
@@ -5073,10 +5073,10 @@
         <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>1.674607097463803</v>
+        <v>1.674607418883084</v>
       </c>
       <c r="E138" t="n">
-        <v>1.702478069971645</v>
+        <v>1.702478148017985</v>
       </c>
       <c r="F138" t="n">
         <v>0.8</v>
@@ -5104,10 +5104,10 @@
         <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2164727013245832</v>
+        <v>0.2164729366957351</v>
       </c>
       <c r="E139" t="n">
-        <v>0.453733017061153</v>
+        <v>0.4537329672101831</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -5135,10 +5135,10 @@
         <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>0.6697985890864586</v>
+        <v>0.6697977693950754</v>
       </c>
       <c r="E140" t="n">
-        <v>0.665740618626701</v>
+        <v>0.6657401777633901</v>
       </c>
       <c r="F140" t="n">
         <v>0.5</v>
@@ -5166,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2953451570639201</v>
+        <v>0.2953450509505036</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4176809561506321</v>
+        <v>0.417680976633975</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -5197,10 +5197,10 @@
         <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>0.5713697312215392</v>
+        <v>0.5713695078195181</v>
       </c>
       <c r="E142" t="n">
-        <v>0.9896410775839045</v>
+        <v>0.9896410174390282</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -5228,10 +5228,10 @@
         <v>4</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3739086501314066</v>
+        <v>0.373908678358872</v>
       </c>
       <c r="E143" t="n">
-        <v>1.103984468253964</v>
+        <v>1.103984390494107</v>
       </c>
       <c r="F143" t="n">
         <v>0.5</v>
@@ -5259,10 +5259,10 @@
         <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>0.8187983448572053</v>
+        <v>0.8187984943627908</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9407237154058496</v>
+        <v>0.9407237354562289</v>
       </c>
       <c r="F144" t="n">
         <v>0.6666666666666666</v>
@@ -5290,10 +5290,10 @@
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>1.498476576538997</v>
+        <v>1.498476657119359</v>
       </c>
       <c r="E145" t="n">
-        <v>2.289451224696933</v>
+        <v>2.28945154432003</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -5321,10 +5321,10 @@
         <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>0.256294231100735</v>
+        <v>0.2562937348921895</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3451546483464416</v>
+        <v>0.345154865559624</v>
       </c>
       <c r="F146" t="n">
         <v>0.7692307692307693</v>
@@ -5352,10 +5352,10 @@
         <v>4</v>
       </c>
       <c r="D147" t="n">
-        <v>0.6113067959881734</v>
+        <v>0.6113068224544</v>
       </c>
       <c r="E147" t="n">
-        <v>1.0781654327359</v>
+        <v>1.078165304013427</v>
       </c>
       <c r="F147" t="n">
         <v>0.3333333333333333</v>
@@ -5383,10 +5383,10 @@
         <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>1.553722694219219</v>
+        <v>1.553724791568159</v>
       </c>
       <c r="E148" t="n">
-        <v>1.553649289687681</v>
+        <v>1.55364719233874</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5414,10 +5414,10 @@
         <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3684881064554044</v>
+        <v>0.368488194164861</v>
       </c>
       <c r="E149" t="n">
-        <v>0.6142012225892538</v>
+        <v>0.6142011763938123</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -5445,10 +5445,10 @@
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>1.314232437568236</v>
+        <v>1.314232498958797</v>
       </c>
       <c r="E150" t="n">
-        <v>1.529154095536486</v>
+        <v>1.529154194033721</v>
       </c>
       <c r="F150" t="n">
         <v>0.7142857142857143</v>
@@ -5476,10 +5476,10 @@
         <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3534589646345223</v>
+        <v>0.3534588662637103</v>
       </c>
       <c r="E151" t="n">
-        <v>0.548794888138561</v>
+        <v>0.548794774177197</v>
       </c>
       <c r="F151" t="n">
         <v>0.6</v>
@@ -5507,10 +5507,10 @@
         <v>4</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4032491404657035</v>
+        <v>0.4032490893758235</v>
       </c>
       <c r="E152" t="n">
-        <v>0.9841490207587765</v>
+        <v>0.9841490556433827</v>
       </c>
       <c r="F152" t="n">
         <v>0.5</v>
@@ -5538,10 +5538,10 @@
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>0.143762803939774</v>
+        <v>0.1437627136671507</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2027716816388829</v>
+        <v>0.2027715536999065</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
@@ -5569,10 +5569,10 @@
         <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>1.676752826565543</v>
+        <v>1.676752864277599</v>
       </c>
       <c r="E154" t="n">
-        <v>1.852981904087292</v>
+        <v>1.852981763654544</v>
       </c>
       <c r="F154" t="n">
         <v>0.75</v>
@@ -5662,10 +5662,10 @@
         <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6719653635518107</v>
+        <v>0.6719654996712584</v>
       </c>
       <c r="E157" t="n">
-        <v>0.7881552004524095</v>
+        <v>0.7881560294118491</v>
       </c>
       <c r="F157" t="n">
         <v>0.4285714285714285</v>
@@ -5693,10 +5693,10 @@
         <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>0.6753731438886285</v>
+        <v>0.675373084427438</v>
       </c>
       <c r="E158" t="n">
-        <v>1.116595631586109</v>
+        <v>1.116595652554338</v>
       </c>
       <c r="F158" t="n">
         <v>0.4444444444444444</v>
@@ -5724,10 +5724,10 @@
         <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4904054357200726</v>
+        <v>0.4904052250808982</v>
       </c>
       <c r="E159" t="n">
-        <v>0.903884557750681</v>
+        <v>0.9038842474814698</v>
       </c>
       <c r="F159" t="n">
         <v>0.25</v>
@@ -5755,10 +5755,10 @@
         <v>4</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4060086069962917</v>
+        <v>0.4060085631371019</v>
       </c>
       <c r="E160" t="n">
-        <v>0.749191069276961</v>
+        <v>0.7491908060329141</v>
       </c>
       <c r="F160" t="n">
         <v>0.2</v>
@@ -5817,10 +5817,10 @@
         <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3734684812885079</v>
+        <v>0.3734683421164114</v>
       </c>
       <c r="E162" t="n">
-        <v>0.7238122813153766</v>
+        <v>0.7238121851947789</v>
       </c>
       <c r="F162" t="n">
         <v>0.5</v>
@@ -5848,10 +5848,10 @@
         <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>0.6326792107736658</v>
+        <v>0.6326793765622987</v>
       </c>
       <c r="E163" t="n">
-        <v>1.28112281358492</v>
+        <v>1.28112280613738</v>
       </c>
       <c r="F163" t="n">
         <v>0.5</v>
@@ -5879,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5871853903983352</v>
+        <v>0.5871853248341511</v>
       </c>
       <c r="E164" t="n">
-        <v>0.8743024829637583</v>
+        <v>0.8743027914507003</v>
       </c>
       <c r="F164" t="n">
         <v>0.5</v>
@@ -5910,10 +5910,10 @@
         <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>0.7033693928372744</v>
+        <v>0.7033694615346041</v>
       </c>
       <c r="E165" t="n">
-        <v>1.127523824029513</v>
+        <v>1.127523873567488</v>
       </c>
       <c r="F165" t="n">
         <v>0.2</v>
@@ -5975,7 +5975,7 @@
         <v>0.270282289556295</v>
       </c>
       <c r="E167" t="n">
-        <v>0.5740129925859377</v>
+        <v>0.574012983924601</v>
       </c>
       <c r="F167" t="n">
         <v>0.6666666666666666</v>
@@ -6003,10 +6003,10 @@
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1779155277270629</v>
+        <v>0.1779117064684869</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2338343512247592</v>
+        <v>0.2338355864803391</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -6034,10 +6034,10 @@
         <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>0.5629525683699396</v>
+        <v>0.5629525438480515</v>
       </c>
       <c r="E169" t="n">
-        <v>0.9759915182202249</v>
+        <v>0.9759914045417396</v>
       </c>
       <c r="F169" t="n">
         <v>0.4285714285714285</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3795342762493137</v>
+        <v>0.3795337978732398</v>
       </c>
       <c r="E170" t="n">
-        <v>0.555532972463321</v>
+        <v>0.5555332992836908</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -6127,10 +6127,10 @@
         <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4623543558501056</v>
+        <v>0.4623545149179987</v>
       </c>
       <c r="E172" t="n">
-        <v>0.6538678006654955</v>
+        <v>0.6538680256214673</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
@@ -6158,10 +6158,10 @@
         <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>0.8688576293430198</v>
+        <v>0.8688540142336394</v>
       </c>
       <c r="E173" t="n">
-        <v>1.192204228106467</v>
+        <v>1.192201936482002</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
@@ -6189,10 +6189,10 @@
         <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2686939838643115</v>
+        <v>0.2686938653149828</v>
       </c>
       <c r="E174" t="n">
-        <v>0.4672011662127146</v>
+        <v>0.467201042435928</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -6220,10 +6220,10 @@
         <v>3</v>
       </c>
       <c r="D175" t="n">
-        <v>0.294870385497288</v>
+        <v>0.294870405687124</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3309160828421445</v>
+        <v>0.33091607824617</v>
       </c>
       <c r="F175" t="n">
         <v>0.5</v>
@@ -6282,10 +6282,10 @@
         <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3306805214657423</v>
+        <v>0.3306803906990854</v>
       </c>
       <c r="E177" t="n">
-        <v>0.6067631794142599</v>
+        <v>0.6067631533291652</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -6313,10 +6313,10 @@
         <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>1.51773306646226</v>
+        <v>1.517732966991375</v>
       </c>
       <c r="E178" t="n">
-        <v>1.445874597118461</v>
+        <v>1.445874757381463</v>
       </c>
       <c r="F178" t="n">
         <v>0.75</v>
@@ -6344,10 +6344,10 @@
         <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1827263995115916</v>
+        <v>0.1827265255500652</v>
       </c>
       <c r="E179" t="n">
-        <v>0.350743158155172</v>
+        <v>0.3507434465844301</v>
       </c>
       <c r="F179" t="n">
         <v>0.3333333333333333</v>
@@ -6378,7 +6378,7 @@
         <v>1.477534855625853</v>
       </c>
       <c r="E180" t="n">
-        <v>1.534255563673087</v>
+        <v>1.53425776509669</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
@@ -6437,10 +6437,10 @@
         <v>4</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2530311364473915</v>
+        <v>0.2530311438127453</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5208692174294663</v>
+        <v>0.5208691300497252</v>
       </c>
       <c r="F182" t="n">
         <v>0.6</v>
@@ -6468,10 +6468,10 @@
         <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>0.6334375802962502</v>
+        <v>0.6334378447509986</v>
       </c>
       <c r="E183" t="n">
-        <v>0.8529850138442664</v>
+        <v>0.8529849597592234</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -6530,10 +6530,10 @@
         <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4689665881969519</v>
+        <v>0.4689664468787907</v>
       </c>
       <c r="E185" t="n">
-        <v>0.8968361808672292</v>
+        <v>0.8968360159284433</v>
       </c>
       <c r="F185" t="n">
         <v>0.125</v>
@@ -6561,10 +6561,10 @@
         <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>0.7015297433474972</v>
+        <v>0.7015296259531204</v>
       </c>
       <c r="E186" t="n">
-        <v>0.9456527807626838</v>
+        <v>0.9456526608920403</v>
       </c>
       <c r="F186" t="n">
         <v>0.25</v>
@@ -6592,10 +6592,10 @@
         <v>4</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2014727018114538</v>
+        <v>0.2014725803684758</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4614083066969576</v>
+        <v>0.4614083015144736</v>
       </c>
       <c r="F187" t="n">
         <v>0.1666666666666667</v>
@@ -6623,10 +6623,10 @@
         <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3208866966373974</v>
+        <v>0.3208865413923133</v>
       </c>
       <c r="E188" t="n">
-        <v>0.4409437690882366</v>
+        <v>0.4409440172697901</v>
       </c>
       <c r="F188" t="n">
         <v>0.3333333333333333</v>
@@ -6654,10 +6654,10 @@
         <v>4</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2405324970482268</v>
+        <v>0.2405326186899332</v>
       </c>
       <c r="E189" t="n">
-        <v>0.5793504651672037</v>
+        <v>0.5793509833769148</v>
       </c>
       <c r="F189" t="n">
         <v>0.5</v>
@@ -6685,10 +6685,10 @@
         <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>0.6455526732219951</v>
+        <v>0.6455526365254745</v>
       </c>
       <c r="E190" t="n">
-        <v>1.017170274328938</v>
+        <v>1.017170246425442</v>
       </c>
       <c r="F190" t="n">
         <v>0.8</v>
@@ -6716,10 +6716,10 @@
         <v>2</v>
       </c>
       <c r="D191" t="n">
-        <v>1.187914007119904</v>
+        <v>1.187913534463897</v>
       </c>
       <c r="E191" t="n">
-        <v>1.187914007119904</v>
+        <v>1.187913534463897</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -6747,10 +6747,10 @@
         <v>4</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4122242428404661</v>
+        <v>0.4122243391482194</v>
       </c>
       <c r="E192" t="n">
-        <v>0.8290856115076264</v>
+        <v>0.829085906221008</v>
       </c>
       <c r="F192" t="n">
         <v>0.5</v>
@@ -6778,10 +6778,10 @@
         <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>0.918712744337407</v>
+        <v>0.9187120826676602</v>
       </c>
       <c r="E193" t="n">
-        <v>0.918712744337407</v>
+        <v>0.9187120826676602</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -6809,10 +6809,10 @@
         <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>0.8728801389198876</v>
+        <v>0.8728801002934136</v>
       </c>
       <c r="E194" t="n">
-        <v>1.241654986070976</v>
+        <v>1.241654924559944</v>
       </c>
       <c r="F194" t="n">
         <v>0.5</v>
@@ -6840,10 +6840,10 @@
         <v>2</v>
       </c>
       <c r="D195" t="n">
-        <v>1.63443579049302</v>
+        <v>1.63443612991072</v>
       </c>
       <c r="E195" t="n">
-        <v>1.704730458591873</v>
+        <v>1.704728256108333</v>
       </c>
       <c r="F195" t="n">
         <v>0.75</v>
@@ -6871,10 +6871,10 @@
         <v>3</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4912155647826102</v>
+        <v>0.4912155438250853</v>
       </c>
       <c r="E196" t="n">
-        <v>1.144413884634235</v>
+        <v>1.144413751195543</v>
       </c>
       <c r="F196" t="n">
         <v>0.75</v>
@@ -6902,10 +6902,10 @@
         <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4854745716095776</v>
+        <v>0.4854747572320283</v>
       </c>
       <c r="E197" t="n">
-        <v>0.686564723357533</v>
+        <v>0.6865649858673203</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -6933,10 +6933,10 @@
         <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4394716350405943</v>
+        <v>0.4394716123795053</v>
       </c>
       <c r="E198" t="n">
-        <v>0.8273012215473944</v>
+        <v>0.8273011296286479</v>
       </c>
       <c r="F198" t="n">
         <v>0.6666666666666666</v>
@@ -7004,13 +7004,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.099974435505296</v>
+        <v>-0.099974289107767</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1158513687297945</v>
+        <v>-0.1158513273593072</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0816290529510683</v>
+        <v>0.0816291952701239</v>
       </c>
     </row>
     <row r="3">
@@ -7020,16 +7020,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.099974435505296</v>
+        <v>-0.099974289107767</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3744331451577568</v>
+        <v>-0.3744331403309703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0043789864991532</v>
+        <v>0.0043789985635497</v>
       </c>
     </row>
     <row r="4">
@@ -7039,16 +7039,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1158513687297946</v>
+        <v>-0.1158513273593072</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3744331451577567</v>
+        <v>-0.3744331403309704</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1505680493661926</v>
+        <v>0.1505681674448483</v>
       </c>
     </row>
     <row r="5">
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0816290529510684</v>
+        <v>0.0816291952701239</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0043789864991532</v>
+        <v>0.0043789985635497</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1505680493661925</v>
+        <v>0.1505681674448483</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'ok': True, 'median_abs_delta_logit': 0.09118048891503494, 'mean_abs_delta_logit': 0.8233057082689532, 'n': 80, 'mask_effective': True}</t>
+          <t>{'ok': True, 'median_abs_delta_logit': 0.09118038273769535, 'mean_abs_delta_logit': 0.8233055879691298, 'n': 80, 'mask_effective': True}</t>
         </is>
       </c>
       <c r="D2" t="b">

--- a/exp_m3_out/assist_09/module3_full.xlsx
+++ b/exp_m3_out/assist_09/module3_full.xlsx
@@ -488,7 +488,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7881541610594204</v>
+        <v>0.7881541586426717</v>
       </c>
       <c r="D3" t="n">
         <v>0.7416125901539515</v>
@@ -507,13 +507,13 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7881289148972148</v>
+        <v>0.7881289374535358</v>
       </c>
       <c r="D4" t="n">
         <v>0.7418219185902681</v>
       </c>
       <c r="E4" t="n">
-        <v>0.459069231995417</v>
+        <v>0.4590692806846758</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +526,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7883337955714254</v>
+        <v>0.7883338076551687</v>
       </c>
       <c r="D5" t="n">
         <v>0.741917067879503</v>
@@ -545,7 +545,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7880946454010528</v>
+        <v>0.7880946486233844</v>
       </c>
       <c r="D6" t="n">
         <v>0.7416696797274924</v>
@@ -583,13 +583,13 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7816478466767726</v>
+        <v>0.7816478676219277</v>
       </c>
       <c r="D8" t="n">
         <v>0.733410721421911</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4677591500857846</v>
+        <v>0.4677591660140256</v>
       </c>
     </row>
     <row r="9">
@@ -602,7 +602,7 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7817709123526235</v>
+        <v>0.7817709139637893</v>
       </c>
       <c r="D9" t="n">
         <v>0.7345144531770348</v>
@@ -621,7 +621,7 @@
         <v>0.3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7821137619861591</v>
+        <v>0.7821137684308221</v>
       </c>
       <c r="D10" t="n">
         <v>0.7339245275837789</v>
@@ -640,7 +640,7 @@
         <v>0.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7828807477892139</v>
+        <v>0.78288075503946</v>
       </c>
       <c r="D11" t="n">
         <v>0.7355991550743116</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7890393065385228</v>
+        <v>0.7890393097608543</v>
       </c>
       <c r="D2" t="n">
         <v>0.742868560771851</v>
@@ -719,7 +719,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7827509667743878</v>
+        <v>0.7827509627464734</v>
       </c>
       <c r="D3" t="n">
         <v>0.7371596034177624</v>
@@ -738,7 +738,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7830391366636476</v>
+        <v>0.7830391398859791</v>
       </c>
       <c r="D4" t="n">
         <v>0.7369502749814459</v>
@@ -757,7 +757,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7831791944994079</v>
+        <v>0.7831791985273222</v>
       </c>
       <c r="D5" t="n">
         <v>0.7376163200060896</v>
@@ -776,13 +776,13 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7829467483898501</v>
+        <v>0.7829467491954329</v>
       </c>
       <c r="D6" t="n">
         <v>0.7370073645549867</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4632594413834835</v>
+        <v>0.4632594735493917</v>
       </c>
     </row>
   </sheetData>
@@ -857,10 +857,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1512454623039485</v>
+        <v>0.1512455266172309</v>
       </c>
       <c r="E2" t="n">
-        <v>0.262299051948838</v>
+        <v>0.2622990289965639</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -888,10 +888,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3665779105887953</v>
+        <v>0.3665779732727403</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8794533908837991</v>
+        <v>0.8794536649845021</v>
       </c>
       <c r="F3" t="n">
         <v>0.6</v>
@@ -919,10 +919,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4126298870391077</v>
+        <v>0.4126298235613701</v>
       </c>
       <c r="E4" t="n">
-        <v>1.059851815637913</v>
+        <v>1.059851730483452</v>
       </c>
       <c r="F4" t="n">
         <v>0.6</v>
@@ -950,10 +950,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.164175242359223</v>
+        <v>1.164174300875894</v>
       </c>
       <c r="E5" t="n">
-        <v>1.646392416723398</v>
+        <v>1.646391085264906</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2947378884787238</v>
+        <v>0.2947379148001052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6634143915628818</v>
+        <v>0.663414409553835</v>
       </c>
       <c r="F6" t="n">
         <v>0.1666666666666667</v>
@@ -1012,10 +1012,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5810277982390522</v>
+        <v>0.5810276139361729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8006091052815862</v>
+        <v>0.8006092469863894</v>
       </c>
       <c r="F7" t="n">
         <v>0.5</v>
@@ -1043,10 +1043,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6266990036328378</v>
+        <v>0.6266991676794232</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9773088227445389</v>
+        <v>0.9773088561497769</v>
       </c>
       <c r="F8" t="n">
         <v>0.6</v>
@@ -1074,10 +1074,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.820025035523151</v>
+        <v>1.820025514621155</v>
       </c>
       <c r="E9" t="n">
-        <v>1.820025035523151</v>
+        <v>1.820023598229076</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1105,10 +1105,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5339241585036881</v>
+        <v>0.5339242422321323</v>
       </c>
       <c r="E10" t="n">
-        <v>1.101833304153173</v>
+        <v>1.101833873810932</v>
       </c>
       <c r="F10" t="n">
         <v>0.25</v>
@@ -1167,10 +1167,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8302776347254063</v>
+        <v>0.8302777135153636</v>
       </c>
       <c r="E12" t="n">
-        <v>1.096167900877571</v>
+        <v>1.096168311273601</v>
       </c>
       <c r="F12" t="n">
         <v>0.5</v>
@@ -1229,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3932334325526721</v>
+        <v>0.3932336441107224</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9284421527170117</v>
+        <v>0.9284420247116484</v>
       </c>
       <c r="F14" t="n">
         <v>0.5</v>
@@ -1291,10 +1291,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.07411628378299</v>
+        <v>1.074116060745762</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1076768098934</v>
+        <v>1.107676514979651</v>
       </c>
       <c r="F16" t="n">
         <v>0.75</v>
@@ -1322,10 +1322,10 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1572667091758251</v>
+        <v>0.1572668304886552</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3438594235974431</v>
+        <v>0.3438595169775933</v>
       </c>
       <c r="F17" t="n">
         <v>0.5</v>
@@ -1353,10 +1353,10 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1.802843263687091</v>
+        <v>1.802842889572682</v>
       </c>
       <c r="E18" t="n">
-        <v>1.850772174971763</v>
+        <v>1.850771877083439</v>
       </c>
       <c r="F18" t="n">
         <v>0.8</v>
@@ -1384,10 +1384,10 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6614575383107535</v>
+        <v>0.6614576216924245</v>
       </c>
       <c r="E19" t="n">
-        <v>1.030613358629495</v>
+        <v>1.030613191298699</v>
       </c>
       <c r="F19" t="n">
         <v>0.5714285714285714</v>
@@ -1446,10 +1446,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3131733545348676</v>
+        <v>0.3131734539703429</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6057027813450842</v>
+        <v>0.6057027853459023</v>
       </c>
       <c r="F21" t="n">
         <v>0.25</v>
@@ -1477,10 +1477,10 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2325603317189987</v>
+        <v>0.2325606099704392</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4073508023766486</v>
+        <v>0.4073507198989967</v>
       </c>
       <c r="F22" t="n">
         <v>0.6666666666666666</v>
@@ -1539,10 +1539,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7593043199819414</v>
+        <v>0.7593042212689883</v>
       </c>
       <c r="E24" t="n">
-        <v>1.082287726579716</v>
+        <v>1.082287687936867</v>
       </c>
       <c r="F24" t="n">
         <v>0.3333333333333333</v>
@@ -1570,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1467885937824474</v>
+        <v>0.1467886420661954</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2757260573020227</v>
+        <v>0.275726144278745</v>
       </c>
       <c r="F25" t="n">
         <v>0.625</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6948923755860803</v>
+        <v>0.6948921594673908</v>
       </c>
       <c r="E26" t="n">
-        <v>1.034101812659773</v>
+        <v>1.034101638726946</v>
       </c>
       <c r="F26" t="n">
         <v>0.5</v>
@@ -1694,10 +1694,10 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2417924614058327</v>
+        <v>0.2417923514554716</v>
       </c>
       <c r="E29" t="n">
-        <v>0.322880799875741</v>
+        <v>0.3228807797714515</v>
       </c>
       <c r="F29" t="n">
         <v>0.8333333333333334</v>
@@ -1725,10 +1725,10 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6579942660673499</v>
+        <v>0.6579941351803134</v>
       </c>
       <c r="E30" t="n">
-        <v>1.304108444704827</v>
+        <v>1.304108485918891</v>
       </c>
       <c r="F30" t="n">
         <v>0.375</v>
@@ -1756,10 +1756,10 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2868629209896341</v>
+        <v>0.2868628607971651</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3654669458827619</v>
+        <v>0.3654668458933606</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3358061851252593</v>
+        <v>0.3358062013018497</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8003483650063025</v>
+        <v>0.80034837146634</v>
       </c>
       <c r="F32" t="n">
         <v>0.4</v>
@@ -1818,10 +1818,10 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.393981809686489</v>
+        <v>0.3939818785059081</v>
       </c>
       <c r="E33" t="n">
-        <v>0.691148281041866</v>
+        <v>0.6911484962136567</v>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
@@ -1849,10 +1849,10 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>1.06879163493145</v>
+        <v>1.068791187731847</v>
       </c>
       <c r="E34" t="n">
-        <v>1.211064732355489</v>
+        <v>1.211063650482598</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -1880,10 +1880,10 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7733114650171818</v>
+        <v>0.773311454744003</v>
       </c>
       <c r="E35" t="n">
-        <v>1.531102848439988</v>
+        <v>1.531103077536259</v>
       </c>
       <c r="F35" t="n">
         <v>0.4285714285714285</v>
@@ -1911,10 +1911,10 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8712971515377973</v>
+        <v>0.8712972520352142</v>
       </c>
       <c r="E36" t="n">
-        <v>1.716907094432355</v>
+        <v>1.716907163030001</v>
       </c>
       <c r="F36" t="n">
         <v>0.6666666666666666</v>
@@ -1942,10 +1942,10 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1096832290192276</v>
+        <v>0.109683244955243</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2094091202292168</v>
+        <v>0.2094091672734587</v>
       </c>
       <c r="F37" t="n">
         <v>0.25</v>
@@ -1973,10 +1973,10 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2754344954877601</v>
+        <v>0.275434038657383</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5164917289049058</v>
+        <v>0.5164914856718615</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2035,10 +2035,10 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8349259038524396</v>
+        <v>0.8349245093612052</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5439125060836224</v>
+        <v>0.5439122024927462</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -2066,10 +2066,10 @@
         <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5821341735003559</v>
+        <v>0.5821343233132912</v>
       </c>
       <c r="E41" t="n">
-        <v>1.242795466974643</v>
+        <v>1.242795579746471</v>
       </c>
       <c r="F41" t="n">
         <v>0.8333333333333334</v>
@@ -2097,10 +2097,10 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1.22136039326929</v>
+        <v>1.221360456822796</v>
       </c>
       <c r="E42" t="n">
-        <v>1.134870643930354</v>
+        <v>1.134870336214966</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -2128,10 +2128,10 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3605627848364238</v>
+        <v>0.3605625580176701</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5099127804026827</v>
+        <v>0.5099124596325249</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2190,10 +2190,10 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6539989534793594</v>
+        <v>0.6539984776103713</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9248884036647168</v>
+        <v>0.9248881101002897</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -2221,10 +2221,10 @@
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4141946459744819</v>
+        <v>0.4141947782919149</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4576237412730391</v>
+        <v>0.4576239765101807</v>
       </c>
       <c r="F46" t="n">
         <v>0.5</v>
@@ -2252,10 +2252,10 @@
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2137469395749997</v>
+        <v>0.2137473241519622</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2574828217854094</v>
+        <v>0.2574839063159667</v>
       </c>
       <c r="F47" t="n">
         <v>0.75</v>
@@ -2283,10 +2283,10 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1789447975466504</v>
+        <v>0.1789455655517614</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1922555519212816</v>
+        <v>0.1922565515387485</v>
       </c>
       <c r="F48" t="n">
         <v>0.5</v>
@@ -2314,10 +2314,10 @@
         <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4307918310911045</v>
+        <v>0.4307918548579339</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9136874803474795</v>
+        <v>0.9136877956788122</v>
       </c>
       <c r="F49" t="n">
         <v>0.1</v>
@@ -2345,10 +2345,10 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4839245650548916</v>
+        <v>0.4839246785484358</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6889510611986562</v>
+        <v>0.6889511250368097</v>
       </c>
       <c r="F50" t="n">
         <v>0.5</v>
@@ -2376,10 +2376,10 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2065907977680043</v>
+        <v>0.2065906936452515</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6771740960412056</v>
+        <v>0.6771739920429893</v>
       </c>
       <c r="F51" t="n">
         <v>0.25</v>
@@ -2407,10 +2407,10 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0.04552073724158889</v>
+        <v>0.0455206423479696</v>
       </c>
       <c r="E52" t="n">
-        <v>0.07489964516880365</v>
+        <v>0.07489922464752737</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2469,10 +2469,10 @@
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2060720888386464</v>
+        <v>0.2060720202353472</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3841527663590047</v>
+        <v>0.3841526049265868</v>
       </c>
       <c r="F54" t="n">
         <v>0.2</v>
@@ -2500,10 +2500,10 @@
         <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6564154689493108</v>
+        <v>0.656415418398246</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9934293712575428</v>
+        <v>0.9934292916874886</v>
       </c>
       <c r="F55" t="n">
         <v>0.5</v>
@@ -2531,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4458768395986037</v>
+        <v>0.4458764794946963</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8597229848814161</v>
+        <v>0.8597231349887571</v>
       </c>
       <c r="F56" t="n">
         <v>0.3333333333333333</v>
@@ -2562,10 +2562,10 @@
         <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2278455568369794</v>
+        <v>0.2278455667712574</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3952255607300867</v>
+        <v>0.3952256362740929</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2593,10 +2593,10 @@
         <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9845286823180112</v>
+        <v>0.9845281440232486</v>
       </c>
       <c r="E58" t="n">
-        <v>1.705253699283634</v>
+        <v>1.705252766929756</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>0.30877678060252</v>
+        <v>0.3087771214064943</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8292226245126313</v>
+        <v>0.8292233423371795</v>
       </c>
       <c r="F60" t="n">
         <v>0.5</v>
@@ -2686,10 +2686,10 @@
         <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3769033841824277</v>
+        <v>0.3769034955070429</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8513879242257244</v>
+        <v>0.8513880748005047</v>
       </c>
       <c r="F61" t="n">
         <v>0.7142857142857143</v>
@@ -2717,10 +2717,10 @@
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5254788345817517</v>
+        <v>0.5254789595682395</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7617600602111718</v>
+        <v>0.761760199351887</v>
       </c>
       <c r="F62" t="n">
         <v>0.5</v>
@@ -2779,10 +2779,10 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1.119993234772829</v>
+        <v>1.119993006491141</v>
       </c>
       <c r="E64" t="n">
-        <v>1.119993234772829</v>
+        <v>1.119993006491141</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5015926169786025</v>
+        <v>0.501592395570592</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6462015480017788</v>
+        <v>0.6462016804829921</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -2872,10 +2872,10 @@
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6022658498830809</v>
+        <v>0.6022657274538903</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6870130788359364</v>
+        <v>0.68701452218298</v>
       </c>
       <c r="F67" t="n">
         <v>0.25</v>
@@ -2903,10 +2903,10 @@
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2234387748212247</v>
+        <v>0.2234388452272563</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3129002344107999</v>
+        <v>0.312900126199066</v>
       </c>
       <c r="F68" t="n">
         <v>0.8</v>
@@ -2934,10 +2934,10 @@
         <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7260096557679531</v>
+        <v>0.7260090628203382</v>
       </c>
       <c r="E69" t="n">
-        <v>1.422460649132467</v>
+        <v>1.422460509730564</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -3027,10 +3027,10 @@
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9746139790455141</v>
+        <v>0.9746146375064528</v>
       </c>
       <c r="E72" t="n">
-        <v>1.379999843230161</v>
+        <v>1.379999027821363</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -3089,10 +3089,10 @@
         <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4034092501247475</v>
+        <v>0.4034092396836244</v>
       </c>
       <c r="E74" t="n">
-        <v>0.865234879003013</v>
+        <v>0.865233504548172</v>
       </c>
       <c r="F74" t="n">
         <v>0.6363636363636364</v>
@@ -3120,10 +3120,10 @@
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2426269825847614</v>
+        <v>0.2426271796329477</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5092266131893793</v>
+        <v>0.5092270160112713</v>
       </c>
       <c r="F75" t="n">
         <v>0.4285714285714285</v>
@@ -3151,10 +3151,10 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8215114695844962</v>
+        <v>0.8215114725321904</v>
       </c>
       <c r="E76" t="n">
-        <v>1.163786982683113</v>
+        <v>1.163786651786595</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6830617511407713</v>
+        <v>0.683061887251925</v>
       </c>
       <c r="E77" t="n">
-        <v>1.185124990950685</v>
+        <v>1.185125173521547</v>
       </c>
       <c r="F77" t="n">
         <v>0.5</v>
@@ -3216,7 +3216,7 @@
         <v>0.5325166329552899</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5323952986381477</v>
+        <v>0.5323949298274873</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -3244,10 +3244,10 @@
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8428855474211842</v>
+        <v>0.8428859026764031</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9179165916671421</v>
+        <v>0.9179167096346345</v>
       </c>
       <c r="F79" t="n">
         <v>0.5</v>
@@ -3275,10 +3275,10 @@
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1.568817539326567</v>
+        <v>1.568817532022821</v>
       </c>
       <c r="E80" t="n">
-        <v>1.703782096193059</v>
+        <v>1.703782085422949</v>
       </c>
       <c r="F80" t="n">
         <v>0.8888888888888888</v>
@@ -3306,10 +3306,10 @@
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7461500791727582</v>
+        <v>0.7461500025396104</v>
       </c>
       <c r="E81" t="n">
-        <v>1.447442143944594</v>
+        <v>1.447441955136926</v>
       </c>
       <c r="F81" t="n">
         <v>0.5</v>
@@ -3337,10 +3337,10 @@
         <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>0.459528648562915</v>
+        <v>0.4595277267515525</v>
       </c>
       <c r="E82" t="n">
-        <v>0.6495814834829723</v>
+        <v>0.6495821355882951</v>
       </c>
       <c r="F82" t="n">
         <v>0.5</v>
@@ -3368,10 +3368,10 @@
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2698860354951864</v>
+        <v>0.2698853259385135</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4267535511944286</v>
+        <v>0.4267532034818814</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -3399,10 +3399,10 @@
         <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8265396150544647</v>
+        <v>0.8265396170361151</v>
       </c>
       <c r="E84" t="n">
-        <v>1.474801397732338</v>
+        <v>1.474801788321888</v>
       </c>
       <c r="F84" t="n">
         <v>0.25</v>
@@ -3461,10 +3461,10 @@
         <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>0.433568826656111</v>
+        <v>0.4335694141222419</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7519572462299687</v>
+        <v>0.7519580439854944</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -3492,10 +3492,10 @@
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5697174091192414</v>
+        <v>0.5697174230263778</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6769127682192484</v>
+        <v>0.6769129361948709</v>
       </c>
       <c r="F87" t="n">
         <v>0.8</v>
@@ -3523,10 +3523,10 @@
         <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>0.435524497822851</v>
+        <v>0.4355252876806531</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7882752907013781</v>
+        <v>0.7882765551175364</v>
       </c>
       <c r="F88" t="n">
         <v>0.75</v>
@@ -3616,10 +3616,10 @@
         <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5236079014129449</v>
+        <v>0.5236076643535678</v>
       </c>
       <c r="E91" t="n">
-        <v>1.056716263435691</v>
+        <v>1.056715749488321</v>
       </c>
       <c r="F91" t="n">
         <v>0.5</v>
@@ -3647,10 +3647,10 @@
         <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>0.625778464766046</v>
+        <v>0.6257783059754152</v>
       </c>
       <c r="E92" t="n">
-        <v>1.149346052959257</v>
+        <v>1.149346207533809</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -3678,10 +3678,10 @@
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0.7547900801857979</v>
+        <v>0.754789773787057</v>
       </c>
       <c r="E93" t="n">
-        <v>0.8467600456477413</v>
+        <v>0.8467597737913101</v>
       </c>
       <c r="F93" t="n">
         <v>0.75</v>
@@ -3709,10 +3709,10 @@
         <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2536866244050661</v>
+        <v>0.2536954832375741</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3905162781656715</v>
+        <v>0.3905110396209782</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -3740,10 +3740,10 @@
         <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7294591607934515</v>
+        <v>0.7294593471950545</v>
       </c>
       <c r="E95" t="n">
-        <v>1.280740303461457</v>
+        <v>1.280740634768001</v>
       </c>
       <c r="F95" t="n">
         <v>0.5</v>
@@ -3833,10 +3833,10 @@
         <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5464043429772827</v>
+        <v>0.5464042481355708</v>
       </c>
       <c r="E98" t="n">
-        <v>0.8093644616848999</v>
+        <v>0.809364308282314</v>
       </c>
       <c r="F98" t="n">
         <v>0.75</v>
@@ -3895,10 +3895,10 @@
         <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3516395703638803</v>
+        <v>0.3516395701316636</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7926036917034052</v>
+        <v>0.7926036732453163</v>
       </c>
       <c r="F100" t="n">
         <v>0.6</v>
@@ -3926,10 +3926,10 @@
         <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>0.8778884288060094</v>
+        <v>0.8778886027051589</v>
       </c>
       <c r="E101" t="n">
-        <v>1.371291809238885</v>
+        <v>1.37129179305788</v>
       </c>
       <c r="F101" t="n">
         <v>0.6666666666666666</v>
@@ -3957,10 +3957,10 @@
         <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>0.6646639050604523</v>
+        <v>0.6646637487994776</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9893360644734536</v>
+        <v>0.9893360450427562</v>
       </c>
       <c r="F102" t="n">
         <v>0.5</v>
@@ -3988,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4907250631812496</v>
+        <v>0.4907250833246024</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8652948430253676</v>
+        <v>0.8652949164998072</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -4019,10 +4019,10 @@
         <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4481564418779246</v>
+        <v>0.4481564405047891</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7292406805921796</v>
+        <v>0.7292407409919826</v>
       </c>
       <c r="F104" t="n">
         <v>0.4</v>
@@ -4050,10 +4050,10 @@
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4003426385086362</v>
+        <v>0.4003425625191319</v>
       </c>
       <c r="E105" t="n">
-        <v>0.7994445252164643</v>
+        <v>0.7994447053630122</v>
       </c>
       <c r="F105" t="n">
         <v>0.4285714285714285</v>
@@ -4081,10 +4081,10 @@
         <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1.053106245361583</v>
+        <v>1.053098213270932</v>
       </c>
       <c r="E106" t="n">
-        <v>1.489295235651686</v>
+        <v>1.489284735338702</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -4112,10 +4112,10 @@
         <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3651048489637302</v>
+        <v>0.3651049088268413</v>
       </c>
       <c r="E107" t="n">
-        <v>0.7158761222038219</v>
+        <v>0.715876300902925</v>
       </c>
       <c r="F107" t="n">
         <v>0.3333333333333333</v>
@@ -4143,10 +4143,10 @@
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1.289105186533281</v>
+        <v>1.289105423677092</v>
       </c>
       <c r="E108" t="n">
-        <v>1.492899631571105</v>
+        <v>1.492899667192952</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2717059063219706</v>
+        <v>0.2717058827539829</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3925146057957392</v>
+        <v>0.3925146255320424</v>
       </c>
       <c r="F109" t="n">
         <v>0.4444444444444444</v>
@@ -4236,10 +4236,10 @@
         <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2608577284606146</v>
+        <v>0.2608577433720781</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5241623260022176</v>
+        <v>0.5241623773413275</v>
       </c>
       <c r="F111" t="n">
         <v>0.3333333333333333</v>
@@ -4298,10 +4298,10 @@
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>0.8759215031954803</v>
+        <v>0.8759218251986027</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9343091793450514</v>
+        <v>0.9343096126892534</v>
       </c>
       <c r="F113" t="n">
         <v>0.6666666666666666</v>
@@ -4329,10 +4329,10 @@
         <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4626486138908843</v>
+        <v>0.4626483909819903</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8013303737706914</v>
+        <v>0.801330519220798</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -4360,10 +4360,10 @@
         <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7384447783836965</v>
+        <v>0.7384452672423425</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7384447783836965</v>
+        <v>0.7384452672423425</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -4422,10 +4422,10 @@
         <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>0.323687096952107</v>
+        <v>0.3236871070672234</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9323578966101078</v>
+        <v>0.9323577899061677</v>
       </c>
       <c r="F117" t="n">
         <v>0.6666666666666666</v>
@@ -4453,10 +4453,10 @@
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>0.979149367688778</v>
+        <v>0.97914995080389</v>
       </c>
       <c r="E118" t="n">
-        <v>1.441597160466</v>
+        <v>1.441597836863561</v>
       </c>
       <c r="F118" t="n">
         <v>0.5</v>
@@ -4546,10 +4546,10 @@
         <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>0.6189353062504616</v>
+        <v>0.6189353412609115</v>
       </c>
       <c r="E121" t="n">
-        <v>1.176943636306105</v>
+        <v>1.176943539395254</v>
       </c>
       <c r="F121" t="n">
         <v>0.4285714285714285</v>
@@ -4577,10 +4577,10 @@
         <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3308459997987168</v>
+        <v>0.3308458260304166</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7623070643486329</v>
+        <v>0.7623071330480362</v>
       </c>
       <c r="F122" t="n">
         <v>0.6666666666666666</v>
@@ -4670,10 +4670,10 @@
         <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6013162571649767</v>
+        <v>0.6013162407962405</v>
       </c>
       <c r="E125" t="n">
-        <v>1.034966965488212</v>
+        <v>1.034966799887217</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -4701,10 +4701,10 @@
         <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>0.5693492570631757</v>
+        <v>0.5693493286266241</v>
       </c>
       <c r="E126" t="n">
-        <v>1.076850238901283</v>
+        <v>1.076850395545543</v>
       </c>
       <c r="F126" t="n">
         <v>0.4</v>
@@ -4732,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>0.7682209693879953</v>
+        <v>0.7682220001981163</v>
       </c>
       <c r="E127" t="n">
-        <v>1.205031155722712</v>
+        <v>1.205030668640065</v>
       </c>
       <c r="F127" t="n">
         <v>0.8</v>
@@ -4794,10 +4794,10 @@
         <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4996647782967007</v>
+        <v>0.4996646454193752</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7066327061073397</v>
+        <v>0.7066325181904241</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
         <v>0.5302713284087134</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8046893103169499</v>
+        <v>0.8046893395072441</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -4856,10 +4856,10 @@
         <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3212498696766594</v>
+        <v>0.3212498912065457</v>
       </c>
       <c r="E131" t="n">
-        <v>0.7162847476057781</v>
+        <v>0.7162846654420234</v>
       </c>
       <c r="F131" t="n">
         <v>0.5</v>
@@ -4887,10 +4887,10 @@
         <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5841736981211109</v>
+        <v>0.5841736216361645</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8358494479675297</v>
+        <v>0.8358493611841225</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>4</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2759744771756603</v>
+        <v>0.2759745124028854</v>
       </c>
       <c r="E133" t="n">
-        <v>0.7205203497432745</v>
+        <v>0.7205203789443304</v>
       </c>
       <c r="F133" t="n">
         <v>0.3333333333333333</v>
@@ -4949,10 +4949,10 @@
         <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>1.361423223519205</v>
+        <v>1.36142307377968</v>
       </c>
       <c r="E134" t="n">
-        <v>1.925343186830558</v>
+        <v>1.92534297506689</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
@@ -4980,10 +4980,10 @@
         <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>0.6182144264844321</v>
+        <v>0.618214417298661</v>
       </c>
       <c r="E135" t="n">
-        <v>0.9159939767038918</v>
+        <v>0.9159940437297521</v>
       </c>
       <c r="F135" t="n">
         <v>0.75</v>
@@ -5011,10 +5011,10 @@
         <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9542011368845107</v>
+        <v>0.9542010837886783</v>
       </c>
       <c r="E136" t="n">
-        <v>1.527235829548379</v>
+        <v>1.527235745553528</v>
       </c>
       <c r="F136" t="n">
         <v>0.6</v>
@@ -5042,10 +5042,10 @@
         <v>4</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2545113639162199</v>
+        <v>0.2545114162866134</v>
       </c>
       <c r="E137" t="n">
-        <v>0.5558669968727968</v>
+        <v>0.555867031191539</v>
       </c>
       <c r="F137" t="n">
         <v>0.4</v>
@@ -5073,10 +5073,10 @@
         <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>1.674607418883084</v>
+        <v>1.674607177300248</v>
       </c>
       <c r="E138" t="n">
-        <v>1.702478148017985</v>
+        <v>1.702478073241056</v>
       </c>
       <c r="F138" t="n">
         <v>0.8</v>
@@ -5104,10 +5104,10 @@
         <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2164729366957351</v>
+        <v>0.2164727444801387</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4537329672101831</v>
+        <v>0.4537331101856183</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -5135,10 +5135,10 @@
         <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>0.6697977693950754</v>
+        <v>0.6697983694996864</v>
       </c>
       <c r="E140" t="n">
-        <v>0.6657401777633901</v>
+        <v>0.6657410987338267</v>
       </c>
       <c r="F140" t="n">
         <v>0.5</v>
@@ -5166,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2953450509505036</v>
+        <v>0.2953451023809042</v>
       </c>
       <c r="E141" t="n">
-        <v>0.417680976633975</v>
+        <v>0.4176810493675449</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -5197,10 +5197,10 @@
         <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>0.5713695078195181</v>
+        <v>0.5713698950094424</v>
       </c>
       <c r="E142" t="n">
-        <v>0.9896410174390282</v>
+        <v>0.9896416880716492</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -5228,10 +5228,10 @@
         <v>4</v>
       </c>
       <c r="D143" t="n">
-        <v>0.373908678358872</v>
+        <v>0.373908891210588</v>
       </c>
       <c r="E143" t="n">
-        <v>1.103984390494107</v>
+        <v>1.103984682214661</v>
       </c>
       <c r="F143" t="n">
         <v>0.5</v>
@@ -5259,10 +5259,10 @@
         <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>0.8187984943627908</v>
+        <v>0.8187983021530377</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9407237354562289</v>
+        <v>0.9407236680866014</v>
       </c>
       <c r="F144" t="n">
         <v>0.6666666666666666</v>
@@ -5321,10 +5321,10 @@
         <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2562937348921895</v>
+        <v>0.2562939751825386</v>
       </c>
       <c r="E146" t="n">
-        <v>0.345154865559624</v>
+        <v>0.3451547197881681</v>
       </c>
       <c r="F146" t="n">
         <v>0.7692307692307693</v>
@@ -5352,10 +5352,10 @@
         <v>4</v>
       </c>
       <c r="D147" t="n">
-        <v>0.6113068224544</v>
+        <v>0.6113068598994674</v>
       </c>
       <c r="E147" t="n">
-        <v>1.078165304013427</v>
+        <v>1.078165633496965</v>
       </c>
       <c r="F147" t="n">
         <v>0.3333333333333333</v>
@@ -5383,10 +5383,10 @@
         <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>1.553724791568159</v>
+        <v>1.553722818110769</v>
       </c>
       <c r="E148" t="n">
-        <v>1.55364719233874</v>
+        <v>1.553649413579231</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5414,10 +5414,10 @@
         <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>0.368488194164861</v>
+        <v>0.3684880848044236</v>
       </c>
       <c r="E149" t="n">
-        <v>0.6142011763938123</v>
+        <v>0.6142011635387392</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -5445,10 +5445,10 @@
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>1.314232498958797</v>
+        <v>1.314232367476253</v>
       </c>
       <c r="E150" t="n">
-        <v>1.529154194033721</v>
+        <v>1.529154133600553</v>
       </c>
       <c r="F150" t="n">
         <v>0.7142857142857143</v>
@@ -5476,10 +5476,10 @@
         <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3534588662637103</v>
+        <v>0.3534589286949884</v>
       </c>
       <c r="E151" t="n">
-        <v>0.548794774177197</v>
+        <v>0.5487949112858875</v>
       </c>
       <c r="F151" t="n">
         <v>0.6</v>
@@ -5507,10 +5507,10 @@
         <v>4</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4032490893758235</v>
+        <v>0.4032489998988038</v>
       </c>
       <c r="E152" t="n">
-        <v>0.9841490556433827</v>
+        <v>0.9841487843194823</v>
       </c>
       <c r="F152" t="n">
         <v>0.5</v>
@@ -5538,10 +5538,10 @@
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1437627136671507</v>
+        <v>0.1437628942129305</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2027715536999065</v>
+        <v>0.202771641673643</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
@@ -5569,10 +5569,10 @@
         <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>1.676752864277599</v>
+        <v>1.676752778691532</v>
       </c>
       <c r="E154" t="n">
-        <v>1.852981763654544</v>
+        <v>1.85298189562408</v>
       </c>
       <c r="F154" t="n">
         <v>0.75</v>
@@ -5600,10 +5600,10 @@
         <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>1.0657643926323</v>
+        <v>1.065764499207608</v>
       </c>
       <c r="E155" t="n">
-        <v>1.296543005819658</v>
+        <v>1.296543156634855</v>
       </c>
       <c r="F155" t="n">
         <v>0.3333333333333333</v>
@@ -5662,10 +5662,10 @@
         <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6719654996712584</v>
+        <v>0.6719656806862997</v>
       </c>
       <c r="E157" t="n">
-        <v>0.7881560294118491</v>
+        <v>0.7881551973415544</v>
       </c>
       <c r="F157" t="n">
         <v>0.4285714285714285</v>
@@ -5693,10 +5693,10 @@
         <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>0.675373084427438</v>
+        <v>0.6753731656755442</v>
       </c>
       <c r="E158" t="n">
-        <v>1.116595652554338</v>
+        <v>1.116595647338299</v>
       </c>
       <c r="F158" t="n">
         <v>0.4444444444444444</v>
@@ -5724,10 +5724,10 @@
         <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4904052250808982</v>
+        <v>0.4904052229745263</v>
       </c>
       <c r="E159" t="n">
-        <v>0.9038842474814698</v>
+        <v>0.903884191602813</v>
       </c>
       <c r="F159" t="n">
         <v>0.25</v>
@@ -5755,10 +5755,10 @@
         <v>4</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4060085631371019</v>
+        <v>0.4060085946850207</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7491908060329141</v>
+        <v>0.7491908559737128</v>
       </c>
       <c r="F160" t="n">
         <v>0.2</v>
@@ -5789,7 +5789,7 @@
         <v>0.3024831050951186</v>
       </c>
       <c r="E161" t="n">
-        <v>0.5195592617273612</v>
+        <v>0.5195592656538071</v>
       </c>
       <c r="F161" t="n">
         <v>0.6</v>
@@ -5817,10 +5817,10 @@
         <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3734683421164114</v>
+        <v>0.3734684416007858</v>
       </c>
       <c r="E162" t="n">
-        <v>0.7238121851947789</v>
+        <v>0.7238122989977598</v>
       </c>
       <c r="F162" t="n">
         <v>0.5</v>
@@ -5848,10 +5848,10 @@
         <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>0.6326793765622987</v>
+        <v>0.6326795232535354</v>
       </c>
       <c r="E163" t="n">
-        <v>1.28112280613738</v>
+        <v>1.281122909228174</v>
       </c>
       <c r="F163" t="n">
         <v>0.5</v>
@@ -5879,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5871853248341511</v>
+        <v>0.5871851835773375</v>
       </c>
       <c r="E164" t="n">
-        <v>0.8743027914507003</v>
+        <v>0.8743025980744387</v>
       </c>
       <c r="F164" t="n">
         <v>0.5</v>
@@ -5910,10 +5910,10 @@
         <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>0.7033694615346041</v>
+        <v>0.7033694199495785</v>
       </c>
       <c r="E165" t="n">
-        <v>1.127523873567488</v>
+        <v>1.127523794346899</v>
       </c>
       <c r="F165" t="n">
         <v>0.2</v>
@@ -5972,10 +5972,10 @@
         <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>0.270282289556295</v>
+        <v>0.270282143320069</v>
       </c>
       <c r="E167" t="n">
-        <v>0.574012983924601</v>
+        <v>0.5740130438452811</v>
       </c>
       <c r="F167" t="n">
         <v>0.6666666666666666</v>
@@ -6003,10 +6003,10 @@
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1779117064684869</v>
+        <v>0.1779153543335134</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2338355864803391</v>
+        <v>0.23383397749366</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -6034,10 +6034,10 @@
         <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>0.5629525438480515</v>
+        <v>0.5629524850571325</v>
       </c>
       <c r="E169" t="n">
-        <v>0.9759914045417396</v>
+        <v>0.9759912497191483</v>
       </c>
       <c r="F169" t="n">
         <v>0.4285714285714285</v>
@@ -6127,10 +6127,10 @@
         <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4623545149179987</v>
+        <v>0.4623543558501056</v>
       </c>
       <c r="E172" t="n">
-        <v>0.6538680256214673</v>
+        <v>0.6538678006654955</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
@@ -6158,10 +6158,10 @@
         <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>0.8688540142336394</v>
+        <v>0.8688576293430198</v>
       </c>
       <c r="E173" t="n">
-        <v>1.192201936482002</v>
+        <v>1.192204228106467</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
@@ -6189,10 +6189,10 @@
         <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2686938653149828</v>
+        <v>0.2686937818539106</v>
       </c>
       <c r="E174" t="n">
-        <v>0.467201042435928</v>
+        <v>0.4672009071922114</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>0.294870405687124</v>
       </c>
       <c r="E175" t="n">
-        <v>0.33091607824617</v>
+        <v>0.3309160845929782</v>
       </c>
       <c r="F175" t="n">
         <v>0.5</v>
@@ -6282,10 +6282,10 @@
         <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3306803906990854</v>
+        <v>0.3306801887988088</v>
       </c>
       <c r="E177" t="n">
-        <v>0.6067631533291652</v>
+        <v>0.6067624092586605</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -6313,10 +6313,10 @@
         <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>1.517732966991375</v>
+        <v>1.51773306646226</v>
       </c>
       <c r="E178" t="n">
-        <v>1.445874757381463</v>
+        <v>1.445874597118461</v>
       </c>
       <c r="F178" t="n">
         <v>0.75</v>
@@ -6344,10 +6344,10 @@
         <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1827265255500652</v>
+        <v>0.1827266152193568</v>
       </c>
       <c r="E179" t="n">
-        <v>0.3507434465844301</v>
+        <v>0.3507433934826343</v>
       </c>
       <c r="F179" t="n">
         <v>0.3333333333333333</v>
@@ -6378,7 +6378,7 @@
         <v>1.477534855625853</v>
       </c>
       <c r="E180" t="n">
-        <v>1.53425776509669</v>
+        <v>1.534255563673087</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
@@ -6437,10 +6437,10 @@
         <v>4</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2530311438127453</v>
+        <v>0.2530311068699366</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5208691300497252</v>
+        <v>0.520869015015463</v>
       </c>
       <c r="F182" t="n">
         <v>0.6</v>
@@ -6468,10 +6468,10 @@
         <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>0.6334378447509986</v>
+        <v>0.6334375133285112</v>
       </c>
       <c r="E183" t="n">
-        <v>0.8529849597592234</v>
+        <v>0.8529849006861097</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -6530,10 +6530,10 @@
         <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4689664468787907</v>
+        <v>0.4689665355306369</v>
       </c>
       <c r="E185" t="n">
-        <v>0.8968360159284433</v>
+        <v>0.8968357149682611</v>
       </c>
       <c r="F185" t="n">
         <v>0.125</v>
@@ -6561,10 +6561,10 @@
         <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>0.7015296259531204</v>
+        <v>0.7015296115474222</v>
       </c>
       <c r="E186" t="n">
-        <v>0.9456526608920403</v>
+        <v>0.9456525023056798</v>
       </c>
       <c r="F186" t="n">
         <v>0.25</v>
@@ -6592,10 +6592,10 @@
         <v>4</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2014725803684758</v>
+        <v>0.2014727327805484</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4614083015144736</v>
+        <v>0.4614083596970749</v>
       </c>
       <c r="F187" t="n">
         <v>0.1666666666666667</v>
@@ -6623,10 +6623,10 @@
         <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3208865413923133</v>
+        <v>0.3208865230885776</v>
       </c>
       <c r="E188" t="n">
-        <v>0.4409440172697901</v>
+        <v>0.4409438504067278</v>
       </c>
       <c r="F188" t="n">
         <v>0.3333333333333333</v>
@@ -6654,10 +6654,10 @@
         <v>4</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2405326186899332</v>
+        <v>0.2405323868220427</v>
       </c>
       <c r="E189" t="n">
-        <v>0.5793509833769148</v>
+        <v>0.5793508605828235</v>
       </c>
       <c r="F189" t="n">
         <v>0.5</v>
@@ -6685,10 +6685,10 @@
         <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>0.6455526365254745</v>
+        <v>0.6455527392525392</v>
       </c>
       <c r="E190" t="n">
-        <v>1.017170246425442</v>
+        <v>1.017170726536161</v>
       </c>
       <c r="F190" t="n">
         <v>0.8</v>
@@ -6716,10 +6716,10 @@
         <v>2</v>
       </c>
       <c r="D191" t="n">
-        <v>1.187913534463897</v>
+        <v>1.187914007119904</v>
       </c>
       <c r="E191" t="n">
-        <v>1.187913534463897</v>
+        <v>1.187914007119904</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -6747,10 +6747,10 @@
         <v>4</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4122243391482194</v>
+        <v>0.4122242490729887</v>
       </c>
       <c r="E192" t="n">
-        <v>0.829085906221008</v>
+        <v>0.8290855303419027</v>
       </c>
       <c r="F192" t="n">
         <v>0.5</v>
@@ -6778,10 +6778,10 @@
         <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>0.9187120826676602</v>
+        <v>0.918712744337407</v>
       </c>
       <c r="E193" t="n">
-        <v>0.9187120826676602</v>
+        <v>0.918712744337407</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -6809,10 +6809,10 @@
         <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>0.8728801002934136</v>
+        <v>0.8728798673805125</v>
       </c>
       <c r="E194" t="n">
-        <v>1.241654924559944</v>
+        <v>1.241654589795744</v>
       </c>
       <c r="F194" t="n">
         <v>0.5</v>
@@ -6840,10 +6840,10 @@
         <v>2</v>
       </c>
       <c r="D195" t="n">
-        <v>1.63443612991072</v>
+        <v>1.634437510240336</v>
       </c>
       <c r="E195" t="n">
-        <v>1.704728256108333</v>
+        <v>1.704726987823211</v>
       </c>
       <c r="F195" t="n">
         <v>0.75</v>
@@ -6871,10 +6871,10 @@
         <v>3</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4912155438250853</v>
+        <v>0.4912155123888002</v>
       </c>
       <c r="E196" t="n">
-        <v>1.144413751195543</v>
+        <v>1.144413479820749</v>
       </c>
       <c r="F196" t="n">
         <v>0.75</v>
@@ -6902,10 +6902,10 @@
         <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4854747572320283</v>
+        <v>0.4854747450052914</v>
       </c>
       <c r="E197" t="n">
-        <v>0.6865649858673203</v>
+        <v>0.6865649685761032</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -6933,10 +6933,10 @@
         <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4394716123795053</v>
+        <v>0.4394719077853549</v>
       </c>
       <c r="E198" t="n">
-        <v>0.8273011296286479</v>
+        <v>0.827301224949364</v>
       </c>
       <c r="F198" t="n">
         <v>0.6666666666666666</v>
@@ -7004,13 +7004,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.099974289107767</v>
+        <v>-0.0999673270327632</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1158513273593072</v>
+        <v>-0.1158511153097845</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0816291952701239</v>
+        <v>0.081629206144438</v>
       </c>
     </row>
     <row r="3">
@@ -7020,16 +7020,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.099974289107767</v>
+        <v>-0.0999673270327632</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3744331403309703</v>
+        <v>-0.3744330776731086</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0043789985635497</v>
+        <v>0.0043791791411894</v>
       </c>
     </row>
     <row r="4">
@@ -7039,16 +7039,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1158513273593072</v>
+        <v>-0.1158511153097846</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3744331403309704</v>
+        <v>-0.3744330776731086</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1505681674448483</v>
+        <v>0.1505682807575427</v>
       </c>
     </row>
     <row r="5">
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0816291952701239</v>
+        <v>0.081629206144438</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0043789985635497</v>
+        <v>0.0043791791411894</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1505681674448483</v>
+        <v>0.1505682807575425</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -7081,7 +7081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7135,6 +7135,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>figs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7147,7 +7152,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'ok': True, 'median_abs_delta_logit': 0.09118038273769535, 'mean_abs_delta_logit': 0.8233055879691298, 'n': 80, 'mask_effective': True}</t>
+          <t>{'ok': True, 'median_abs_delta_logit': 0.09118047955917175, 'mean_abs_delta_logit': 0.8233056140366394, 'n': 80, 'mask_effective': True}</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -7171,6 +7176,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>If mask_effective=False, Exp-3B/3C are skipped as model-head defect.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>{'single_keep': ['qnoise_curve.png', 'qnoise_hard_curve.png', 'attribution_violin.png', 'attribution_ridge.png', 'interaction_heatmap.png', 'interaction_network.png', 'interaction_heatmap_global.png'], 'combo_added': ['fig_m3_qnoise_combo.png', 'fig_m3_interaction_global_combo.png']}</t>
         </is>
       </c>
     </row>

--- a/exp_m3_out/assist_09/module3_full.xlsx
+++ b/exp_m3_out/assist_09/module3_full.xlsx
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7890393081496887</v>
+        <v>0.7890393041217743</v>
       </c>
       <c r="D2" t="n">
         <v>0.742868560771851</v>
@@ -488,7 +488,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7881541586426717</v>
+        <v>0.7881541618650032</v>
       </c>
       <c r="D3" t="n">
         <v>0.7416125901539515</v>
@@ -507,7 +507,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7881289374535358</v>
+        <v>0.7881289318144555</v>
       </c>
       <c r="D4" t="n">
         <v>0.7418219185902681</v>
@@ -545,7 +545,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7880946486233844</v>
+        <v>0.7880946470122185</v>
       </c>
       <c r="D6" t="n">
         <v>0.7416696797274924</v>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7890393065385228</v>
+        <v>0.7890393025106084</v>
       </c>
       <c r="D7" t="n">
         <v>0.742868560771851</v>
@@ -583,7 +583,7 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7816478676219277</v>
+        <v>0.7816478668163449</v>
       </c>
       <c r="D8" t="n">
         <v>0.733410721421911</v>
@@ -602,7 +602,7 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7817709139637893</v>
+        <v>0.7817709107414577</v>
       </c>
       <c r="D9" t="n">
         <v>0.7345144531770348</v>
@@ -621,7 +621,7 @@
         <v>0.3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7821137684308221</v>
+        <v>0.7821137652084906</v>
       </c>
       <c r="D10" t="n">
         <v>0.7339245275837789</v>
@@ -640,7 +640,7 @@
         <v>0.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.78288075503946</v>
+        <v>0.7828807502059625</v>
       </c>
       <c r="D11" t="n">
         <v>0.7355991550743116</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7890393097608543</v>
+        <v>0.7890393017050255</v>
       </c>
       <c r="D2" t="n">
         <v>0.742868560771851</v>
@@ -719,7 +719,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7827509627464734</v>
+        <v>0.7827509611353076</v>
       </c>
       <c r="D3" t="n">
         <v>0.7371596034177624</v>
@@ -738,7 +738,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7830391398859791</v>
+        <v>0.7830391527753054</v>
       </c>
       <c r="D4" t="n">
         <v>0.7369502749814459</v>
@@ -757,7 +757,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7831791985273222</v>
+        <v>0.7831791872491618</v>
       </c>
       <c r="D5" t="n">
         <v>0.7376163200060896</v>
@@ -776,7 +776,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7829467491954329</v>
+        <v>0.7829467524177645</v>
       </c>
       <c r="D6" t="n">
         <v>0.7370073645549867</v>
@@ -857,10 +857,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1512455266172309</v>
+        <v>0.1512455845230346</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2622990289965639</v>
+        <v>0.2622991443518891</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -888,10 +888,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3665779732727403</v>
+        <v>0.3665778801288572</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8794536649845021</v>
+        <v>0.8794534033170976</v>
       </c>
       <c r="F3" t="n">
         <v>0.6</v>
@@ -919,10 +919,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4126298235613701</v>
+        <v>0.41262974769364</v>
       </c>
       <c r="E4" t="n">
-        <v>1.059851730483452</v>
+        <v>1.059851806009408</v>
       </c>
       <c r="F4" t="n">
         <v>0.6</v>
@@ -981,10 +981,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2947379148001052</v>
+        <v>0.2947378078834764</v>
       </c>
       <c r="E6" t="n">
-        <v>0.663414409553835</v>
+        <v>0.6634142254550757</v>
       </c>
       <c r="F6" t="n">
         <v>0.1666666666666667</v>
@@ -1012,10 +1012,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5810276139361729</v>
+        <v>0.5810277759666364</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8006092469863894</v>
+        <v>0.8006093516819369</v>
       </c>
       <c r="F7" t="n">
         <v>0.5</v>
@@ -1043,10 +1043,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6266991676794232</v>
+        <v>0.6266989919572075</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9773088561497769</v>
+        <v>0.9773086957872151</v>
       </c>
       <c r="F8" t="n">
         <v>0.6</v>
@@ -1074,10 +1074,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.820025514621155</v>
+        <v>1.820025035523151</v>
       </c>
       <c r="E9" t="n">
-        <v>1.820023598229076</v>
+        <v>1.820024316876104</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1105,10 +1105,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5339242422321323</v>
+        <v>0.5339243920355229</v>
       </c>
       <c r="E10" t="n">
-        <v>1.101833873810932</v>
+        <v>1.101833452434166</v>
       </c>
       <c r="F10" t="n">
         <v>0.25</v>
@@ -1167,10 +1167,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8302777135153636</v>
+        <v>0.8302776347254063</v>
       </c>
       <c r="E12" t="n">
-        <v>1.096168311273601</v>
+        <v>1.096167900877571</v>
       </c>
       <c r="F12" t="n">
         <v>0.5</v>
@@ -1229,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3932336441107224</v>
+        <v>0.3932335315519826</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9284420247116484</v>
+        <v>0.9284427536514278</v>
       </c>
       <c r="F14" t="n">
         <v>0.5</v>
@@ -1291,10 +1291,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.074116060745762</v>
+        <v>1.07411635195921</v>
       </c>
       <c r="E16" t="n">
-        <v>1.107676514979651</v>
+        <v>1.107676898147891</v>
       </c>
       <c r="F16" t="n">
         <v>0.75</v>
@@ -1322,10 +1322,10 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1572668304886552</v>
+        <v>0.157266838119992</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3438595169775933</v>
+        <v>0.3438595140947605</v>
       </c>
       <c r="F17" t="n">
         <v>0.5</v>
@@ -1353,10 +1353,10 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1.802842889572682</v>
+        <v>1.80284318392781</v>
       </c>
       <c r="E18" t="n">
-        <v>1.850771877083439</v>
+        <v>1.850772124588538</v>
       </c>
       <c r="F18" t="n">
         <v>0.8</v>
@@ -1384,10 +1384,10 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6614576216924245</v>
+        <v>0.6614575440937533</v>
       </c>
       <c r="E19" t="n">
-        <v>1.030613191298699</v>
+        <v>1.030613599496718</v>
       </c>
       <c r="F19" t="n">
         <v>0.5714285714285714</v>
@@ -1446,10 +1446,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3131734539703429</v>
+        <v>0.3131734782780963</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6057027853459023</v>
+        <v>0.6057025186851657</v>
       </c>
       <c r="F21" t="n">
         <v>0.25</v>
@@ -1477,10 +1477,10 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2325606099704392</v>
+        <v>0.2325602452114361</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4073507198989967</v>
+        <v>0.4073505346316859</v>
       </c>
       <c r="F22" t="n">
         <v>0.6666666666666666</v>
@@ -1539,10 +1539,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7593042212689883</v>
+        <v>0.7593042624720471</v>
       </c>
       <c r="E24" t="n">
-        <v>1.082287687936867</v>
+        <v>1.082287629662985</v>
       </c>
       <c r="F24" t="n">
         <v>0.3333333333333333</v>
@@ -1570,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1467886420661954</v>
+        <v>0.1467885708324868</v>
       </c>
       <c r="E25" t="n">
-        <v>0.275726144278745</v>
+        <v>0.2757263113746964</v>
       </c>
       <c r="F25" t="n">
         <v>0.625</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6948921594673908</v>
+        <v>0.6948923228049807</v>
       </c>
       <c r="E26" t="n">
-        <v>1.034101638726946</v>
+        <v>1.034101770181403</v>
       </c>
       <c r="F26" t="n">
         <v>0.5</v>
@@ -1694,10 +1694,10 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2417923514554716</v>
+        <v>0.2417923849927016</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3228807797714515</v>
+        <v>0.3228806648299914</v>
       </c>
       <c r="F29" t="n">
         <v>0.8333333333333334</v>
@@ -1725,10 +1725,10 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6579941351803134</v>
+        <v>0.6579941371639324</v>
       </c>
       <c r="E30" t="n">
-        <v>1.304108485918891</v>
+        <v>1.304108336481268</v>
       </c>
       <c r="F30" t="n">
         <v>0.375</v>
@@ -1756,10 +1756,10 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2868628607971651</v>
+        <v>0.286862630318916</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3654668458933606</v>
+        <v>0.3654664630318299</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3358062013018497</v>
+        <v>0.3358061343566897</v>
       </c>
       <c r="E32" t="n">
-        <v>0.80034837146634</v>
+        <v>0.8003483696501226</v>
       </c>
       <c r="F32" t="n">
         <v>0.4</v>
@@ -1818,10 +1818,10 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3939818785059081</v>
+        <v>0.3939818911741489</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6911484962136567</v>
+        <v>0.6911484748281215</v>
       </c>
       <c r="F33" t="n">
         <v>0.5</v>
@@ -1849,10 +1849,10 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>1.068791187731847</v>
+        <v>1.068791593293996</v>
       </c>
       <c r="E34" t="n">
-        <v>1.211063650482598</v>
+        <v>1.211064661641327</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -1880,10 +1880,10 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.773311454744003</v>
+        <v>0.7733114921155577</v>
       </c>
       <c r="E35" t="n">
-        <v>1.531103077536259</v>
+        <v>1.531103065398069</v>
       </c>
       <c r="F35" t="n">
         <v>0.4285714285714285</v>
@@ -1911,10 +1911,10 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8712972520352142</v>
+        <v>0.8712972080430346</v>
       </c>
       <c r="E36" t="n">
-        <v>1.716907163030001</v>
+        <v>1.71690757340027</v>
       </c>
       <c r="F36" t="n">
         <v>0.6666666666666666</v>
@@ -1942,10 +1942,10 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.109683244955243</v>
+        <v>0.1096831759695758</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2094091672734587</v>
+        <v>0.2094091160731457</v>
       </c>
       <c r="F37" t="n">
         <v>0.25</v>
@@ -1973,10 +1973,10 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.275434038657383</v>
+        <v>0.2754343406033902</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5164914856718615</v>
+        <v>0.5164916966313913</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2035,10 +2035,10 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8349245093612052</v>
+        <v>0.8349257569288181</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5439122024927462</v>
+        <v>0.5439125026378834</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -2066,10 +2066,10 @@
         <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5821343233132912</v>
+        <v>0.5821347098575739</v>
       </c>
       <c r="E41" t="n">
-        <v>1.242795579746471</v>
+        <v>1.242797015096438</v>
       </c>
       <c r="F41" t="n">
         <v>0.8333333333333334</v>
@@ -2097,10 +2097,10 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1.221360456822796</v>
+        <v>1.221360771284732</v>
       </c>
       <c r="E42" t="n">
-        <v>1.134870336214966</v>
+        <v>1.134870722427267</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -2128,10 +2128,10 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3605625580176701</v>
+        <v>0.360562688118705</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5099124596325249</v>
+        <v>0.5099126436231731</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2190,10 +2190,10 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6539984776103713</v>
+        <v>0.6539986640163039</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9248881101002897</v>
+        <v>0.9248883737153847</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -2221,10 +2221,10 @@
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4141947782919149</v>
+        <v>0.4141943542654007</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4576239765101807</v>
+        <v>0.4576236090892515</v>
       </c>
       <c r="F46" t="n">
         <v>0.5</v>
@@ -2252,10 +2252,10 @@
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2137473241519622</v>
+        <v>0.2137475283102057</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2574839063159667</v>
+        <v>0.257484054334655</v>
       </c>
       <c r="F47" t="n">
         <v>0.75</v>
@@ -2283,10 +2283,10 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1789455655517614</v>
+        <v>0.1789449061668312</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1922565515387485</v>
+        <v>0.1922555968557339</v>
       </c>
       <c r="F48" t="n">
         <v>0.5</v>
@@ -2314,10 +2314,10 @@
         <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4307918548579339</v>
+        <v>0.4307918607705774</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9136877956788122</v>
+        <v>0.913687696686622</v>
       </c>
       <c r="F49" t="n">
         <v>0.1</v>
@@ -2345,10 +2345,10 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4839246785484358</v>
+        <v>0.4839247655491836</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6889511250368097</v>
+        <v>0.688950803238365</v>
       </c>
       <c r="F50" t="n">
         <v>0.5</v>
@@ -2376,10 +2376,10 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2065906936452515</v>
+        <v>0.2065908077303777</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6771739920429893</v>
+        <v>0.6771736809937642</v>
       </c>
       <c r="F51" t="n">
         <v>0.25</v>
@@ -2407,10 +2407,10 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0455206423479696</v>
+        <v>0.04552083012674546</v>
       </c>
       <c r="E52" t="n">
-        <v>0.07489922464752737</v>
+        <v>0.07489980593597922</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2469,10 +2469,10 @@
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2060720202353472</v>
+        <v>0.2060720576173927</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3841526049265868</v>
+        <v>0.3841526144037152</v>
       </c>
       <c r="F54" t="n">
         <v>0.2</v>
@@ -2500,10 +2500,10 @@
         <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0.656415418398246</v>
+        <v>0.6564154997890957</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9934292916874886</v>
+        <v>0.9934294770034039</v>
       </c>
       <c r="F55" t="n">
         <v>0.5</v>
@@ -2531,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4458764794946963</v>
+        <v>0.4458765707973247</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8597231349887571</v>
+        <v>0.8597232994313196</v>
       </c>
       <c r="F56" t="n">
         <v>0.3333333333333333</v>
@@ -2562,10 +2562,10 @@
         <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2278455667712574</v>
+        <v>0.2278455293688271</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3952256362740929</v>
+        <v>0.3952255391152759</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2593,10 +2593,10 @@
         <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9845281440232486</v>
+        <v>0.9845286823180112</v>
       </c>
       <c r="E58" t="n">
-        <v>1.705252766929756</v>
+        <v>1.705253699283634</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2624,10 +2624,10 @@
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9618048179813201</v>
+        <v>0.9618049150834438</v>
       </c>
       <c r="E59" t="n">
-        <v>1.087387882801208</v>
+        <v>1.087387998819888</v>
       </c>
       <c r="F59" t="n">
         <v>0.6</v>
@@ -2655,10 +2655,10 @@
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3087771214064943</v>
+        <v>0.3087766735192291</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8292233423371795</v>
+        <v>0.8292222541711907</v>
       </c>
       <c r="F60" t="n">
         <v>0.5</v>
@@ -2686,10 +2686,10 @@
         <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3769034955070429</v>
+        <v>0.3769034257918462</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8513880748005047</v>
+        <v>0.8513879712183638</v>
       </c>
       <c r="F61" t="n">
         <v>0.7142857142857143</v>
@@ -2717,10 +2717,10 @@
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5254789595682395</v>
+        <v>0.5254788346731237</v>
       </c>
       <c r="E62" t="n">
-        <v>0.761760199351887</v>
+        <v>0.7617600603677667</v>
       </c>
       <c r="F62" t="n">
         <v>0.5</v>
@@ -2779,10 +2779,10 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1.119993006491141</v>
+        <v>1.119993234772829</v>
       </c>
       <c r="E64" t="n">
-        <v>1.119993006491141</v>
+        <v>1.119993234772829</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>0.501592395570592</v>
+        <v>0.5015926430313488</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6462016804829921</v>
+        <v>0.6462015907370801</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -2872,10 +2872,10 @@
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6022657274538903</v>
+        <v>0.6022658655218658</v>
       </c>
       <c r="E67" t="n">
-        <v>0.68701452218298</v>
+        <v>0.6870145978027477</v>
       </c>
       <c r="F67" t="n">
         <v>0.25</v>
@@ -2903,10 +2903,10 @@
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2234388452272563</v>
+        <v>0.2234389280950212</v>
       </c>
       <c r="E68" t="n">
-        <v>0.312900126199066</v>
+        <v>0.3129002882938852</v>
       </c>
       <c r="F68" t="n">
         <v>0.8</v>
@@ -2934,10 +2934,10 @@
         <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7260090628203382</v>
+        <v>0.726009018116706</v>
       </c>
       <c r="E69" t="n">
-        <v>1.422460509730564</v>
+        <v>1.42246048708308</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -3027,10 +3027,10 @@
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9746146375064528</v>
+        <v>0.9746146772429004</v>
       </c>
       <c r="E72" t="n">
-        <v>1.379999027821363</v>
+        <v>1.379999087352796</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -3089,10 +3089,10 @@
         <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4034092396836244</v>
+        <v>0.403409258438316</v>
       </c>
       <c r="E74" t="n">
-        <v>0.865233504548172</v>
+        <v>0.8652348625790696</v>
       </c>
       <c r="F74" t="n">
         <v>0.6363636363636364</v>
@@ -3120,10 +3120,10 @@
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2426271796329477</v>
+        <v>0.242627223112768</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5092270160112713</v>
+        <v>0.5092268179945613</v>
       </c>
       <c r="F75" t="n">
         <v>0.4285714285714285</v>
@@ -3151,10 +3151,10 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8215114725321904</v>
+        <v>0.8215114546206325</v>
       </c>
       <c r="E76" t="n">
-        <v>1.163786651786595</v>
+        <v>1.163787007948642</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>0.683061887251925</v>
+        <v>0.6830618040505192</v>
       </c>
       <c r="E77" t="n">
-        <v>1.185125173521547</v>
+        <v>1.185125238752996</v>
       </c>
       <c r="F77" t="n">
         <v>0.5</v>
@@ -3213,10 +3213,10 @@
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>0.5325166329552899</v>
+        <v>0.5325161972707674</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5323949298274873</v>
+        <v>0.532394125385759</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -3244,10 +3244,10 @@
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8428859026764031</v>
+        <v>0.842885922177691</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9179167096346345</v>
+        <v>0.9179166473427497</v>
       </c>
       <c r="F79" t="n">
         <v>0.5</v>
@@ -3275,10 +3275,10 @@
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1.568817532022821</v>
+        <v>1.568817610500098</v>
       </c>
       <c r="E80" t="n">
-        <v>1.703782085422949</v>
+        <v>1.703781926078165</v>
       </c>
       <c r="F80" t="n">
         <v>0.8888888888888888</v>
@@ -3306,10 +3306,10 @@
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7461500025396104</v>
+        <v>0.7461501151232098</v>
       </c>
       <c r="E81" t="n">
-        <v>1.447441955136926</v>
+        <v>1.447442196230096</v>
       </c>
       <c r="F81" t="n">
         <v>0.5</v>
@@ -3337,10 +3337,10 @@
         <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4595277267515525</v>
+        <v>0.4595293109468276</v>
       </c>
       <c r="E82" t="n">
-        <v>0.6495821355882951</v>
+        <v>0.6495797934203541</v>
       </c>
       <c r="F82" t="n">
         <v>0.5</v>
@@ -3368,10 +3368,10 @@
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2698853259385135</v>
+        <v>0.2698858778161096</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4267532034818814</v>
+        <v>0.4267534739245785</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -3399,10 +3399,10 @@
         <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8265396170361151</v>
+        <v>0.826539834097226</v>
       </c>
       <c r="E84" t="n">
-        <v>1.474801788321888</v>
+        <v>1.474801778094484</v>
       </c>
       <c r="F84" t="n">
         <v>0.25</v>
@@ -3461,10 +3461,10 @@
         <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4335694141222419</v>
+        <v>0.4335692118466492</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7519580439854944</v>
+        <v>0.7519579947973776</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -3492,10 +3492,10 @@
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5697174230263778</v>
+        <v>0.5697175778772896</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6769129361948709</v>
+        <v>0.676912955517817</v>
       </c>
       <c r="F87" t="n">
         <v>0.8</v>
@@ -3523,10 +3523,10 @@
         <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4355252876806531</v>
+        <v>0.4355252151340766</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7882765551175364</v>
+        <v>0.7882763951672511</v>
       </c>
       <c r="F88" t="n">
         <v>0.75</v>
@@ -3616,10 +3616,10 @@
         <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5236076643535678</v>
+        <v>0.5236080777342927</v>
       </c>
       <c r="E91" t="n">
-        <v>1.056715749488321</v>
+        <v>1.056716397723318</v>
       </c>
       <c r="F91" t="n">
         <v>0.5</v>
@@ -3647,10 +3647,10 @@
         <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>0.6257783059754152</v>
+        <v>0.6257782435557533</v>
       </c>
       <c r="E92" t="n">
-        <v>1.149346207533809</v>
+        <v>1.149346080061835</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -3678,10 +3678,10 @@
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0.754789773787057</v>
+        <v>0.7547899434963137</v>
       </c>
       <c r="E93" t="n">
-        <v>0.8467597737913101</v>
+        <v>0.8467600147840627</v>
       </c>
       <c r="F93" t="n">
         <v>0.75</v>
@@ -3709,10 +3709,10 @@
         <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2536954832375741</v>
+        <v>0.2536866244050661</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3905110396209782</v>
+        <v>0.3905162781656715</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -3740,10 +3740,10 @@
         <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7294593471950545</v>
+        <v>0.7294622487569592</v>
       </c>
       <c r="E95" t="n">
-        <v>1.280740634768001</v>
+        <v>1.280743884310134</v>
       </c>
       <c r="F95" t="n">
         <v>0.5</v>
@@ -3833,10 +3833,10 @@
         <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5464042481355708</v>
+        <v>0.5464043030055584</v>
       </c>
       <c r="E98" t="n">
-        <v>0.809364308282314</v>
+        <v>0.8093645390943218</v>
       </c>
       <c r="F98" t="n">
         <v>0.75</v>
@@ -3895,10 +3895,10 @@
         <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3516395701316636</v>
+        <v>0.3516387807240686</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7926036732453163</v>
+        <v>0.7926022087884658</v>
       </c>
       <c r="F100" t="n">
         <v>0.6</v>
@@ -3926,10 +3926,10 @@
         <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>0.8778886027051589</v>
+        <v>0.877888489678213</v>
       </c>
       <c r="E101" t="n">
-        <v>1.37129179305788</v>
+        <v>1.371292193540663</v>
       </c>
       <c r="F101" t="n">
         <v>0.6666666666666666</v>
@@ -3957,10 +3957,10 @@
         <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>0.6646637487994776</v>
+        <v>0.6646638107030974</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9893360450427562</v>
+        <v>0.9893361653880118</v>
       </c>
       <c r="F102" t="n">
         <v>0.5</v>
@@ -3988,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4907250833246024</v>
+        <v>0.4907250958416978</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8652949164998072</v>
+        <v>0.8652946843313508</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -4019,10 +4019,10 @@
         <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4481564405047891</v>
+        <v>0.4481563793088911</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7292407409919826</v>
+        <v>0.7292403805980491</v>
       </c>
       <c r="F104" t="n">
         <v>0.4</v>
@@ -4050,10 +4050,10 @@
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4003425625191319</v>
+        <v>0.4003426549502183</v>
       </c>
       <c r="E105" t="n">
-        <v>0.7994447053630122</v>
+        <v>0.7994445182880198</v>
       </c>
       <c r="F105" t="n">
         <v>0.4285714285714285</v>
@@ -4081,10 +4081,10 @@
         <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1.053098213270932</v>
+        <v>1.053098618104968</v>
       </c>
       <c r="E106" t="n">
-        <v>1.489284735338702</v>
+        <v>1.489284449081937</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -4112,10 +4112,10 @@
         <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3651049088268413</v>
+        <v>0.3651048823467133</v>
       </c>
       <c r="E107" t="n">
-        <v>0.715876300902925</v>
+        <v>0.715876302078971</v>
       </c>
       <c r="F107" t="n">
         <v>0.3333333333333333</v>
@@ -4143,10 +4143,10 @@
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1.289105423677092</v>
+        <v>1.289105578409134</v>
       </c>
       <c r="E108" t="n">
-        <v>1.492899667192952</v>
+        <v>1.492900249469205</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2717058827539829</v>
+        <v>0.2717058350612568</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3925146255320424</v>
+        <v>0.3925144723824829</v>
       </c>
       <c r="F109" t="n">
         <v>0.4444444444444444</v>
@@ -4236,10 +4236,10 @@
         <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2608577433720781</v>
+        <v>0.260857704277515</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5241623773413275</v>
+        <v>0.5241623188594763</v>
       </c>
       <c r="F111" t="n">
         <v>0.3333333333333333</v>
@@ -4298,10 +4298,10 @@
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>0.8759218251986027</v>
+        <v>0.8759217064060385</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9343096126892534</v>
+        <v>0.9343093942095068</v>
       </c>
       <c r="F113" t="n">
         <v>0.6666666666666666</v>
@@ -4329,10 +4329,10 @@
         <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4626483909819903</v>
+        <v>0.4626486138908843</v>
       </c>
       <c r="E114" t="n">
-        <v>0.801330519220798</v>
+        <v>0.8013303737706914</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -4360,10 +4360,10 @@
         <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7384452672423425</v>
+        <v>0.7384447783836965</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7384452672423425</v>
+        <v>0.7384447783836965</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -4422,10 +4422,10 @@
         <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3236871070672234</v>
+        <v>0.3236871511890108</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9323577899061677</v>
+        <v>0.932357800586006</v>
       </c>
       <c r="F117" t="n">
         <v>0.6666666666666666</v>
@@ -4453,10 +4453,10 @@
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>0.97914995080389</v>
+        <v>0.979149975580996</v>
       </c>
       <c r="E118" t="n">
-        <v>1.441597836863561</v>
+        <v>1.441597882456356</v>
       </c>
       <c r="F118" t="n">
         <v>0.5</v>
@@ -4546,10 +4546,10 @@
         <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>0.6189353412609115</v>
+        <v>0.6189353620001095</v>
       </c>
       <c r="E121" t="n">
-        <v>1.176943539395254</v>
+        <v>1.176943628256902</v>
       </c>
       <c r="F121" t="n">
         <v>0.4285714285714285</v>
@@ -4577,10 +4577,10 @@
         <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3308458260304166</v>
+        <v>0.3308459522695582</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7623071330480362</v>
+        <v>0.7623069711220029</v>
       </c>
       <c r="F122" t="n">
         <v>0.6666666666666666</v>
@@ -4670,10 +4670,10 @@
         <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6013162407962405</v>
+        <v>0.6013163697257579</v>
       </c>
       <c r="E125" t="n">
-        <v>1.034966799887217</v>
+        <v>1.034967095591676</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -4701,10 +4701,10 @@
         <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>0.5693493286266241</v>
+        <v>0.5693493494336689</v>
       </c>
       <c r="E126" t="n">
-        <v>1.076850395545543</v>
+        <v>1.076850234267828</v>
       </c>
       <c r="F126" t="n">
         <v>0.4</v>
@@ -4732,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>0.7682220001981163</v>
+        <v>0.7682210640330612</v>
       </c>
       <c r="E127" t="n">
-        <v>1.205030668640065</v>
+        <v>1.20503086970778</v>
       </c>
       <c r="F127" t="n">
         <v>0.8</v>
@@ -4794,10 +4794,10 @@
         <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4996646454193752</v>
+        <v>0.4996649443934317</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7066325181904241</v>
+        <v>0.7066329410035895</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4825,10 +4825,10 @@
         <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>0.5302713284087134</v>
+        <v>0.5302712125617579</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8046893395072441</v>
+        <v>0.8046894158700884</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -4856,10 +4856,10 @@
         <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3212498912065457</v>
+        <v>0.3212497573275214</v>
       </c>
       <c r="E131" t="n">
-        <v>0.7162846654420234</v>
+        <v>0.7162846111935243</v>
       </c>
       <c r="F131" t="n">
         <v>0.5</v>
@@ -4887,10 +4887,10 @@
         <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5841736216361645</v>
+        <v>0.5841755509225717</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8358493611841225</v>
+        <v>0.8358525253750198</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>4</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2759745124028854</v>
+        <v>0.2759744769463194</v>
       </c>
       <c r="E133" t="n">
-        <v>0.7205203789443304</v>
+        <v>0.7205205470158996</v>
       </c>
       <c r="F133" t="n">
         <v>0.3333333333333333</v>
@@ -4949,10 +4949,10 @@
         <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>1.36142307377968</v>
+        <v>1.361422961876851</v>
       </c>
       <c r="E134" t="n">
-        <v>1.92534297506689</v>
+        <v>1.925342816812393</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
@@ -4980,10 +4980,10 @@
         <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>0.618214417298661</v>
+        <v>0.6182144859356451</v>
       </c>
       <c r="E135" t="n">
-        <v>0.9159940437297521</v>
+        <v>0.915994045899172</v>
       </c>
       <c r="F135" t="n">
         <v>0.75</v>
@@ -5011,10 +5011,10 @@
         <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9542010837886783</v>
+        <v>0.9542010581765585</v>
       </c>
       <c r="E136" t="n">
-        <v>1.527235745553528</v>
+        <v>1.527235755125785</v>
       </c>
       <c r="F136" t="n">
         <v>0.6</v>
@@ -5042,10 +5042,10 @@
         <v>4</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2545114162866134</v>
+        <v>0.2545114268980129</v>
       </c>
       <c r="E137" t="n">
-        <v>0.555867031191539</v>
+        <v>0.5558670305931638</v>
       </c>
       <c r="F137" t="n">
         <v>0.4</v>
@@ -5073,10 +5073,10 @@
         <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>1.674607177300248</v>
+        <v>1.674607104710739</v>
       </c>
       <c r="E138" t="n">
-        <v>1.702478073241056</v>
+        <v>1.702478093310743</v>
       </c>
       <c r="F138" t="n">
         <v>0.8</v>
@@ -5104,10 +5104,10 @@
         <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2164727444801387</v>
+        <v>0.2164729510809924</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4537331101856183</v>
+        <v>0.4537330116191231</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -5135,10 +5135,10 @@
         <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>0.6697983694996864</v>
+        <v>0.6697962392366238</v>
       </c>
       <c r="E140" t="n">
-        <v>0.6657410987338267</v>
+        <v>0.6657429810595028</v>
       </c>
       <c r="F140" t="n">
         <v>0.5</v>
@@ -5166,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2953451023809042</v>
+        <v>0.2953452342095919</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4176810493675449</v>
+        <v>0.4176812358014629</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -5197,10 +5197,10 @@
         <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>0.5713698950094424</v>
+        <v>0.5713697917055574</v>
       </c>
       <c r="E142" t="n">
-        <v>0.9896416880716492</v>
+        <v>0.9896409281680566</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -5228,10 +5228,10 @@
         <v>4</v>
       </c>
       <c r="D143" t="n">
-        <v>0.373908891210588</v>
+        <v>0.3739087366954741</v>
       </c>
       <c r="E143" t="n">
-        <v>1.103984682214661</v>
+        <v>1.103984825275386</v>
       </c>
       <c r="F143" t="n">
         <v>0.5</v>
@@ -5259,10 +5259,10 @@
         <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>0.8187983021530377</v>
+        <v>0.8187987832535342</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9407236680866014</v>
+        <v>0.9407238023187349</v>
       </c>
       <c r="F144" t="n">
         <v>0.6666666666666666</v>
@@ -5290,10 +5290,10 @@
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>1.498476657119359</v>
+        <v>1.49847657653901</v>
       </c>
       <c r="E145" t="n">
-        <v>2.28945154432003</v>
+        <v>2.2894513860182</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -5321,10 +5321,10 @@
         <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2562939751825386</v>
+        <v>0.2562938756000575</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3451547197881681</v>
+        <v>0.3451547873838111</v>
       </c>
       <c r="F146" t="n">
         <v>0.7692307692307693</v>
@@ -5352,10 +5352,10 @@
         <v>4</v>
       </c>
       <c r="D147" t="n">
-        <v>0.6113068598994674</v>
+        <v>0.6113068745593322</v>
       </c>
       <c r="E147" t="n">
-        <v>1.078165633496965</v>
+        <v>1.07816545601463</v>
       </c>
       <c r="F147" t="n">
         <v>0.3333333333333333</v>
@@ -5383,10 +5383,10 @@
         <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>1.553722818110769</v>
+        <v>1.553722942002313</v>
       </c>
       <c r="E148" t="n">
-        <v>1.553649413579231</v>
+        <v>1.553649537470775</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5414,10 +5414,10 @@
         <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3684880848044236</v>
+        <v>0.368488172091092</v>
       </c>
       <c r="E149" t="n">
-        <v>0.6142011635387392</v>
+        <v>0.6142012832747112</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -5445,10 +5445,10 @@
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>1.314232367476253</v>
+        <v>1.31423238650483</v>
       </c>
       <c r="E150" t="n">
-        <v>1.529154133600553</v>
+        <v>1.529153487976919</v>
       </c>
       <c r="F150" t="n">
         <v>0.7142857142857143</v>
@@ -5476,10 +5476,10 @@
         <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3534589286949884</v>
+        <v>0.3534590176180164</v>
       </c>
       <c r="E151" t="n">
-        <v>0.5487949112858875</v>
+        <v>0.5487949308136415</v>
       </c>
       <c r="F151" t="n">
         <v>0.6</v>
@@ -5507,10 +5507,10 @@
         <v>4</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4032489998988038</v>
+        <v>0.4032489806512277</v>
       </c>
       <c r="E152" t="n">
-        <v>0.9841487843194823</v>
+        <v>0.9841487965330371</v>
       </c>
       <c r="F152" t="n">
         <v>0.5</v>
@@ -5538,10 +5538,10 @@
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1437628942129305</v>
+        <v>0.1437622512193577</v>
       </c>
       <c r="E153" t="n">
-        <v>0.202771641673643</v>
+        <v>0.202772079969811</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
@@ -5569,10 +5569,10 @@
         <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>1.676752778691532</v>
+        <v>1.676752849149423</v>
       </c>
       <c r="E154" t="n">
-        <v>1.85298189562408</v>
+        <v>1.852981778804483</v>
       </c>
       <c r="F154" t="n">
         <v>0.75</v>
@@ -5600,10 +5600,10 @@
         <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>1.065764499207608</v>
+        <v>1.065764445569628</v>
       </c>
       <c r="E155" t="n">
-        <v>1.296543156634855</v>
+        <v>1.296543080731501</v>
       </c>
       <c r="F155" t="n">
         <v>0.3333333333333333</v>
@@ -5662,10 +5662,10 @@
         <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6719656806862997</v>
+        <v>0.6719654658462446</v>
       </c>
       <c r="E157" t="n">
-        <v>0.7881551973415544</v>
+        <v>0.7881553644764733</v>
       </c>
       <c r="F157" t="n">
         <v>0.4285714285714285</v>
@@ -5693,10 +5693,10 @@
         <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>0.6753731656755442</v>
+        <v>0.675373095875466</v>
       </c>
       <c r="E158" t="n">
-        <v>1.116595647338299</v>
+        <v>1.116595671401903</v>
       </c>
       <c r="F158" t="n">
         <v>0.4444444444444444</v>
@@ -5724,10 +5724,10 @@
         <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4904052229745263</v>
+        <v>0.4904054119111813</v>
       </c>
       <c r="E159" t="n">
-        <v>0.903884191602813</v>
+        <v>0.903884534583959</v>
       </c>
       <c r="F159" t="n">
         <v>0.25</v>
@@ -5755,10 +5755,10 @@
         <v>4</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4060085946850207</v>
+        <v>0.4060084972066424</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7491908559737128</v>
+        <v>0.7491909062968374</v>
       </c>
       <c r="F160" t="n">
         <v>0.2</v>
@@ -5817,10 +5817,10 @@
         <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3734684416007858</v>
+        <v>0.3734685550174244</v>
       </c>
       <c r="E162" t="n">
-        <v>0.7238122989977598</v>
+        <v>0.7238121955445083</v>
       </c>
       <c r="F162" t="n">
         <v>0.5</v>
@@ -5848,10 +5848,10 @@
         <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>0.6326795232535354</v>
+        <v>0.6326792024404775</v>
       </c>
       <c r="E163" t="n">
-        <v>1.281122909228174</v>
+        <v>1.281122543026705</v>
       </c>
       <c r="F163" t="n">
         <v>0.5</v>
@@ -5879,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5871851835773375</v>
+        <v>0.5871852749859284</v>
       </c>
       <c r="E164" t="n">
-        <v>0.8743025980744387</v>
+        <v>0.8743027314566465</v>
       </c>
       <c r="F164" t="n">
         <v>0.5</v>
@@ -5910,10 +5910,10 @@
         <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>0.7033694199495785</v>
+        <v>0.7033694111609473</v>
       </c>
       <c r="E165" t="n">
-        <v>1.127523794346899</v>
+        <v>1.127523734146432</v>
       </c>
       <c r="F165" t="n">
         <v>0.2</v>
@@ -5972,10 +5972,10 @@
         <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>0.270282143320069</v>
+        <v>0.2702821370198467</v>
       </c>
       <c r="E167" t="n">
-        <v>0.5740130438452811</v>
+        <v>0.5740130449459445</v>
       </c>
       <c r="F167" t="n">
         <v>0.6666666666666666</v>
@@ -6003,10 +6003,10 @@
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1779153543335134</v>
+        <v>0.177915331123955</v>
       </c>
       <c r="E168" t="n">
-        <v>0.23383397749366</v>
+        <v>0.2338344476053657</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -6034,10 +6034,10 @@
         <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>0.5629524850571325</v>
+        <v>0.5629525441907794</v>
       </c>
       <c r="E169" t="n">
-        <v>0.9759912497191483</v>
+        <v>0.9759913157341708</v>
       </c>
       <c r="F169" t="n">
         <v>0.4285714285714285</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3795337978732398</v>
+        <v>0.3795340489011796</v>
       </c>
       <c r="E170" t="n">
-        <v>0.5555332992836908</v>
+        <v>0.5555332115419537</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -6127,10 +6127,10 @@
         <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4623543558501056</v>
+        <v>0.4623548599773164</v>
       </c>
       <c r="E172" t="n">
-        <v>0.6538678006654955</v>
+        <v>0.6538685136090342</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
@@ -6189,10 +6189,10 @@
         <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2686937818539106</v>
+        <v>0.2686939192865676</v>
       </c>
       <c r="E174" t="n">
-        <v>0.4672009071922114</v>
+        <v>0.4672008976240691</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -6220,10 +6220,10 @@
         <v>3</v>
       </c>
       <c r="D175" t="n">
-        <v>0.294870405687124</v>
+        <v>0.2948705646367786</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3309160845929782</v>
+        <v>0.3309160851435813</v>
       </c>
       <c r="F175" t="n">
         <v>0.5</v>
@@ -6282,10 +6282,10 @@
         <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3306801887988088</v>
+        <v>0.330680131311978</v>
       </c>
       <c r="E177" t="n">
-        <v>0.6067624092586605</v>
+        <v>0.60676254651544</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -6313,10 +6313,10 @@
         <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>1.51773306646226</v>
+        <v>1.517733000148339</v>
       </c>
       <c r="E178" t="n">
-        <v>1.445874597118461</v>
+        <v>1.445874595374203</v>
       </c>
       <c r="F178" t="n">
         <v>0.75</v>
@@ -6344,10 +6344,10 @@
         <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1827266152193568</v>
+        <v>0.1827265165499811</v>
       </c>
       <c r="E179" t="n">
-        <v>0.3507433934826343</v>
+        <v>0.350743075601041</v>
       </c>
       <c r="F179" t="n">
         <v>0.3333333333333333</v>
@@ -6437,10 +6437,10 @@
         <v>4</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2530311068699366</v>
+        <v>0.2530312558624301</v>
       </c>
       <c r="E182" t="n">
-        <v>0.520869015015463</v>
+        <v>0.520869237929765</v>
       </c>
       <c r="F182" t="n">
         <v>0.6</v>
@@ -6468,10 +6468,10 @@
         <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>0.6334375133285112</v>
+        <v>0.6334377592836981</v>
       </c>
       <c r="E183" t="n">
-        <v>0.8529849006861097</v>
+        <v>0.8529849772385678</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -6530,10 +6530,10 @@
         <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4689665355306369</v>
+        <v>0.4689665446970177</v>
       </c>
       <c r="E185" t="n">
-        <v>0.8968357149682611</v>
+        <v>0.8968361717961836</v>
       </c>
       <c r="F185" t="n">
         <v>0.125</v>
@@ -6561,10 +6561,10 @@
         <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>0.7015296115474222</v>
+        <v>0.7015298485155533</v>
       </c>
       <c r="E186" t="n">
-        <v>0.9456525023056798</v>
+        <v>0.9456527884828626</v>
       </c>
       <c r="F186" t="n">
         <v>0.25</v>
@@ -6592,10 +6592,10 @@
         <v>4</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2014727327805484</v>
+        <v>0.201472654686545</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4614083596970749</v>
+        <v>0.4614084010135271</v>
       </c>
       <c r="F187" t="n">
         <v>0.1666666666666667</v>
@@ -6623,10 +6623,10 @@
         <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3208865230885776</v>
+        <v>0.3208865435019214</v>
       </c>
       <c r="E188" t="n">
-        <v>0.4409438504067278</v>
+        <v>0.4409436162926111</v>
       </c>
       <c r="F188" t="n">
         <v>0.3333333333333333</v>
@@ -6654,10 +6654,10 @@
         <v>4</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2405323868220427</v>
+        <v>0.2405324869676208</v>
       </c>
       <c r="E189" t="n">
-        <v>0.5793508605828235</v>
+        <v>0.579350819026036</v>
       </c>
       <c r="F189" t="n">
         <v>0.5</v>
@@ -6685,10 +6685,10 @@
         <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>0.6455527392525392</v>
+        <v>0.6455525490494881</v>
       </c>
       <c r="E190" t="n">
-        <v>1.017170726536161</v>
+        <v>1.017170233541825</v>
       </c>
       <c r="F190" t="n">
         <v>0.8</v>
@@ -6716,10 +6716,10 @@
         <v>2</v>
       </c>
       <c r="D191" t="n">
-        <v>1.187914007119904</v>
+        <v>1.187914309601033</v>
       </c>
       <c r="E191" t="n">
-        <v>1.187914007119904</v>
+        <v>1.187913784427319</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -6747,10 +6747,10 @@
         <v>4</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4122242490729887</v>
+        <v>0.4122241807137217</v>
       </c>
       <c r="E192" t="n">
-        <v>0.8290855303419027</v>
+        <v>0.8290854962713035</v>
       </c>
       <c r="F192" t="n">
         <v>0.5</v>
@@ -6778,10 +6778,10 @@
         <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>0.918712744337407</v>
+        <v>0.9187122019752484</v>
       </c>
       <c r="E193" t="n">
-        <v>0.918712744337407</v>
+        <v>0.9187122019752484</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -6809,10 +6809,10 @@
         <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>0.8728798673805125</v>
+        <v>0.8728801002934136</v>
       </c>
       <c r="E194" t="n">
-        <v>1.241654589795744</v>
+        <v>1.241654924559944</v>
       </c>
       <c r="F194" t="n">
         <v>0.5</v>
@@ -6840,10 +6840,10 @@
         <v>2</v>
       </c>
       <c r="D195" t="n">
-        <v>1.634437510240336</v>
+        <v>1.634435882527833</v>
       </c>
       <c r="E195" t="n">
-        <v>1.704726987823211</v>
+        <v>1.704730450293701</v>
       </c>
       <c r="F195" t="n">
         <v>0.75</v>
@@ -6871,10 +6871,10 @@
         <v>3</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4912155123888002</v>
+        <v>0.4912155333463233</v>
       </c>
       <c r="E196" t="n">
-        <v>1.144413479820749</v>
+        <v>1.144413577650991</v>
       </c>
       <c r="F196" t="n">
         <v>0.75</v>
@@ -6902,10 +6902,10 @@
         <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4854747450052914</v>
+        <v>0.485474446009978</v>
       </c>
       <c r="E197" t="n">
-        <v>0.6865649685761032</v>
+        <v>0.6865645457328757</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -6933,10 +6933,10 @@
         <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4394719077853549</v>
+        <v>0.4394716537710868</v>
       </c>
       <c r="E198" t="n">
-        <v>0.827301224949364</v>
+        <v>0.8273009581579536</v>
       </c>
       <c r="F198" t="n">
         <v>0.6666666666666666</v>
@@ -7004,13 +7004,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0999673270327632</v>
+        <v>-0.0999743286872814</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1158511153097845</v>
+        <v>-0.1158513687297945</v>
       </c>
       <c r="E2" t="n">
-        <v>0.081629206144438</v>
+        <v>0.0816290750411717</v>
       </c>
     </row>
     <row r="3">
@@ -7020,16 +7020,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0999673270327632</v>
+        <v>-0.0999743286872814</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3744330776731086</v>
+        <v>-0.3744331759314007</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0043791791411894</v>
+        <v>0.0043789959536311</v>
       </c>
     </row>
     <row r="4">
@@ -7039,16 +7039,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1158511153097846</v>
+        <v>-0.1158513687297945</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3744330776731086</v>
+        <v>-0.3744331759314008</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1505682807575427</v>
+        <v>0.1505680454651672</v>
       </c>
     </row>
     <row r="5">
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.081629206144438</v>
+        <v>0.0816290750411718</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0043791791411894</v>
+        <v>0.004378995953631</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1505682807575425</v>
+        <v>0.1505680454651671</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'ok': True, 'median_abs_delta_logit': 0.09118047955917175, 'mean_abs_delta_logit': 0.8233056140366394, 'n': 80, 'mask_effective': True}</t>
+          <t>{'ok': True, 'median_abs_delta_logit': 0.09118051861403642, 'mean_abs_delta_logit': 0.8233056478647217, 'n': 80, 'mask_effective': True}</t>
         </is>
       </c>
       <c r="D2" t="b">
